--- a/docs/qa/Plan_de_pruebas_Sprint_1-4.xlsx
+++ b/docs/qa/Plan_de_pruebas_Sprint_1-4.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defectos y pendientes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parte A - Manuales'!$A$1:$M$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parte A - Manuales'!$A$1:$M$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pasos TC'!$A$1:$E$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parte B - Automatizados'!$A$1:$L$431</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defectos y pendientes'!$A$1:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defectos y pendientes'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Casos manuales (TC) y automatizados (TA) de los Sprint 1, 2 y 3. Se actualiza con los contadores de las hojas.</t>
+          <t>Casos manuales (TC) y automatizados (TA) de los Sprint 1 a 4 (el Sprint 4 todavía sin desarrollo: casos Pendientes). Se actualiza con los contadores de las hojas.</t>
         </is>
       </c>
     </row>
@@ -538,23 +538,23 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$147,B5)</f>
+        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$195,B5)</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B5,'Parte A - Manuales'!$J$2:$J$147,"OK")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B5,'Parte A - Manuales'!$J$2:$J$147,"Falla")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"Falla")</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B5,'Parte A - Manuales'!$J$2:$J$147,"Bloqueado")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B5,'Parte A - Manuales'!$J$2:$J$147,"Pendiente")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"Pendiente")</f>
         <v/>
       </c>
     </row>
@@ -570,55 +570,55 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$147,B6)</f>
+        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$195,B6)</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B6,'Parte A - Manuales'!$J$2:$J$147,"OK")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B6,'Parte A - Manuales'!$J$2:$J$147,"Falla")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"Falla")</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B6,'Parte A - Manuales'!$J$2:$J$147,"Bloqueado")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$147,B6,'Parte A - Manuales'!$J$2:$J$147,"Pendiente")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"Pendiente")</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Automatizados (TA)</t>
+          <t>Manuales (TC)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sprint 1-2</t>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$431,B7)</f>
+        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$195,B7)</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B7,'Parte B - Automatizados'!$J$2:$J$431,"OK")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B7,'Parte B - Automatizados'!$J$2:$J$431,"Falla")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"Falla")</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B7,'Parte B - Automatizados'!$J$2:$J$431,"Bloqueado")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B7,'Parte B - Automatizados'!$J$2:$J$431,"Pendiente")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"Pendiente")</f>
         <v/>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 1-2</t>
         </is>
       </c>
       <c r="C8" s="3">
@@ -655,126 +655,172 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Automatizados (TA)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C9" s="3">
+        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$431,B9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"OK")</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"Falla")</f>
+        <v/>
+      </c>
+      <c r="F9" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"Bloqueado")</f>
+        <v/>
+      </c>
+      <c r="G9" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"Pendiente")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
-      <c r="C9" s="4">
-        <f>SUM(C5:C8)</f>
+      <c r="B10" s="4" t="inlineStr"/>
+      <c r="C10" s="4">
+        <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D9" s="4">
-        <f>SUM(D5:D8)</f>
+      <c r="D10" s="4">
+        <f>SUM(D5:D9)</f>
         <v/>
       </c>
-      <c r="E9" s="4">
-        <f>SUM(E5:E8)</f>
+      <c r="E10" s="4">
+        <f>SUM(E5:E9)</f>
         <v/>
       </c>
-      <c r="F9" s="4">
-        <f>SUM(F5:F8)</f>
+      <c r="F10" s="4">
+        <f>SUM(F5:F9)</f>
         <v/>
       </c>
-      <c r="G9" s="4">
-        <f>SUM(G5:G8)</f>
+      <c r="G10" s="4">
+        <f>SUM(G5:G9)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Última ejecución (2026-10-09, rama dev)</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Backend: 246 pruebas unitarias y 240 de integración, todas OK.</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Última ejecución (2026-10-12, rama dev)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Frontend: 20 archivos / 51 pruebas y build de producción, OK.</t>
+          <t>Backend: 246 pruebas unitarias y 240 de integración, todas OK.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UI en navegador real (Playwright): 33 de 33 verificaciones OK en el flujo de Sprint 3.</t>
+          <t>Frontend: 20 archivos / 51 pruebas y build de producción, OK.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Prueba de humo por rol (Referente, Directora, Escucha, Coordinador): 11 de 15 pantallas OK; las 4 restantes son /inicio (ver Defectos y pendientes).</t>
+          <t>UI en navegador real (Playwright): 33 de 33 verificaciones OK el 2026-10-09; no se volvió a correr el 2026-10-12 (necesita el stack completo).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Prueba de humo por rol (Referente, Directora, Escucha, Coordinador): 11 de 15 pantallas OK; las 4 restantes son /inicio (ver Defectos y pendientes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>QA manual Sprint 1-2 (TC-01 a TC-40): 40 de 40 OK el 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sprint 4: casos derivados de los criterios de aceptación de Jira, todos Pendientes hasta que haya desarrollo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Épicas / historias cubiertas</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Sprint 1-2: EP-01 Fichas de personas · EP-02 Observaciones e historia de vida · EP-03 Cuentas, roles y notificaciones · EP-10 Asistencia · EP-12 Casa de Convivencia</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Sprint 3: EP-04 Calendario general y personal (SCRUM-15, 16, 17) · EP-05 Colaboradores (SCRUM-18, 19) y visitas de la Casa de Convivencia (SCRUM-74)</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Hojas</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sprint 4: EP-10 Asistencia (SCRUM-54, 55, 56, 57) · Medicación (SCRUM-59, 60, 61, 71, 75)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Parte A - Manuales: un caso por fila con sus pasos; el estado se completa desde la lista desplegable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pasos TC: los TC del Sprint 1-2 con una fila por paso (#, Paso, Dato, Esperamos).</t>
+          <t>Sprint 3: EP-04 Calendario general y personal (SCRUM-15, 16, 17) · EP-05 Colaboradores (SCRUM-18, 19) y visitas de la Casa de Convivencia (SCRUM-74)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Parte B - Automatizados: un test xUnit por fila. Sprint 3 deriva su descripción del nombre del test.</t>
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Hojas</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
+        <is>
+          <t>Parte A - Manuales: un caso por fila con sus pasos; el estado se completa desde la lista desplegable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Pasos TC: los TC del Sprint 1-2 con una fila por paso (#, Paso, Dato, Esperamos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Parte B - Automatizados: un test xUnit por fila. Sprint 3 deriva su descripción del nombre del test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Defectos y pendientes: hallazgos de la ejecución y decisiones abiertas.</t>
         </is>
@@ -791,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3338,7 +3384,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -3401,7 +3447,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -3464,7 +3510,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -3527,7 +3573,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -3590,7 +3636,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -3653,7 +3699,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3716,7 +3762,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -3779,7 +3825,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3842,7 +3888,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -3905,7 +3951,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3968,7 +4014,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -4031,7 +4077,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -4094,7 +4140,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -4157,7 +4203,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -4220,7 +4266,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -4283,7 +4329,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -4346,7 +4392,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -4409,7 +4455,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -4472,7 +4518,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -4535,7 +4581,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -4598,7 +4644,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -4661,7 +4707,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -4724,7 +4770,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -4787,7 +4833,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4850,7 +4896,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -4913,7 +4959,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4976,7 +5022,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -5039,7 +5085,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -5102,7 +5148,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -5165,7 +5211,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -5228,7 +5274,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -5291,7 +5337,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -5354,7 +5400,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -5417,7 +5463,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -5480,7 +5526,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -5543,7 +5589,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -5606,7 +5652,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -5669,7 +5715,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -5732,7 +5778,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -5795,7 +5841,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5858,7 +5904,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -5921,7 +5967,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -5984,7 +6030,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -6614,7 +6660,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -7059,7 +7105,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -7122,7 +7168,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -7185,7 +7231,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -7248,7 +7294,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -7311,7 +7357,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -7374,7 +7420,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -7437,7 +7483,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -7500,7 +7546,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -7563,7 +7609,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -7626,7 +7672,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -7689,7 +7735,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -7752,7 +7798,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -7815,7 +7861,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -7878,7 +7924,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -7941,7 +7987,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -8004,7 +8050,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -8067,7 +8113,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -8130,7 +8176,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -8193,7 +8239,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -8256,7 +8302,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -8319,7 +8365,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -8382,7 +8428,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -8445,7 +8491,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -8508,7 +8554,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -8571,7 +8617,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -8634,7 +8680,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -8697,7 +8743,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -8760,7 +8806,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -8823,7 +8869,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -8886,7 +8932,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -8949,7 +8995,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -9012,7 +9058,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -9075,7 +9121,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -9138,7 +9184,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -9201,7 +9247,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -9264,7 +9310,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -9327,7 +9373,7 @@
       </c>
       <c r="K137" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L137" s="7" t="inlineStr">
@@ -9390,7 +9436,7 @@
       </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L138" s="7" t="inlineStr">
@@ -9453,7 +9499,7 @@
       </c>
       <c r="K139" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L139" s="7" t="inlineStr">
@@ -9516,7 +9562,7 @@
       </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L140" s="7" t="inlineStr">
@@ -9579,7 +9625,7 @@
       </c>
       <c r="K141" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L141" s="7" t="inlineStr">
@@ -9642,7 +9688,7 @@
       </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L142" s="7" t="inlineStr">
@@ -9705,7 +9751,7 @@
       </c>
       <c r="K143" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L143" s="7" t="inlineStr">
@@ -9768,7 +9814,7 @@
       </c>
       <c r="K144" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L144" s="7" t="inlineStr">
@@ -9831,7 +9877,7 @@
       </c>
       <c r="K145" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L145" s="7" t="inlineStr">
@@ -9894,7 +9940,7 @@
       </c>
       <c r="K146" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L146" s="7" t="inlineStr">
@@ -9957,7 +10003,7 @@
       </c>
       <c r="K147" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L147" s="7" t="inlineStr">
@@ -9967,10 +10013,2681 @@
       </c>
       <c r="M147" s="7" t="inlineStr"/>
     </row>
+    <row r="148">
+      <c r="A148" s="7" t="inlineStr">
+        <is>
+          <t>TC-147</t>
+        </is>
+      </c>
+      <c r="B148" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C148" s="7" t="inlineStr">
+        <is>
+          <t>Registro de asistencia diaria (EP-10) (SCRUM-54)</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>Registrar asistencia diaria de Hogar de día con personas con ficha</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>Criterios 1 y 2: se registra asistencia por actividad marcando personas con ficha existente.</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Hay al menos 3 personas con ficha.</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>1. Ingresar como Referente y abrir la pantalla de asistencia diaria  →  Se muestra el registro del día con las actividades disponibles
+2. Elegir la actividad Hogar de día y marcar 2 personas con ficha  →  Las personas quedan marcadas como presentes
+3. Guardar la asistencia  →  Mensaje de éxito; al reabrir el día las 2 personas figuran presentes</t>
+        </is>
+      </c>
+      <c r="I148" s="7" t="inlineStr"/>
+      <c r="J148" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K148" s="7" t="inlineStr"/>
+      <c r="L148" s="7" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
+        <is>
+          <t>TC-148</t>
+        </is>
+      </c>
+      <c r="B149" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C149" s="7" t="inlineStr">
+        <is>
+          <t>Registro de asistencia diaria (EP-10) (SCRUM-54)</t>
+        </is>
+      </c>
+      <c r="D149" s="7" t="inlineStr">
+        <is>
+          <t>Registrar asistencia diaria de la Casona</t>
+        </is>
+      </c>
+      <c r="E149" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 1: la Casona tiene registro diario propio.</t>
+        </is>
+      </c>
+      <c r="F149" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Hay residentes de Casona con ficha.</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="H149" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir la asistencia diaria y elegir la actividad Casona  →  Se listan las personas candidatas de Casona
+2. Marcar a un residente y guardar  →  El residente figura presente en la Casona y no en el Hogar de día</t>
+        </is>
+      </c>
+      <c r="I149" s="7" t="inlineStr"/>
+      <c r="J149" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K149" s="7" t="inlineStr"/>
+      <c r="L149" s="7" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="7" t="inlineStr">
+        <is>
+          <t>TC-149</t>
+        </is>
+      </c>
+      <c r="B150" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C150" s="7" t="inlineStr">
+        <is>
+          <t>Registro de asistencia diaria (EP-10) (SCRUM-54)</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>Registrar un conteo de personas sin ficha (anónimas)</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 3: además de las personas con ficha, se puede cargar un conteo de anónimos.</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="H150" s="7" t="inlineStr">
+        <is>
+          <t>1. En la actividad Hogar de día cargar un conteo de personas sin ficha  →  El campo acepta el número
+2. Guardar y reabrir el día  →  El conteo de 4 anónimos se conserva junto con las personas con ficha
+3. Probar con una cantidad negativa  →  El sistema rechaza el valor con un mensaje de validación</t>
+        </is>
+      </c>
+      <c r="I150" s="7" t="inlineStr"/>
+      <c r="J150" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K150" s="7" t="inlineStr"/>
+      <c r="L150" s="7" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="7" t="inlineStr">
+        <is>
+          <t>TC-150</t>
+        </is>
+      </c>
+      <c r="B151" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C151" s="7" t="inlineStr">
+        <is>
+          <t>Registro de asistencia diaria (EP-10) (SCRUM-54)</t>
+        </is>
+      </c>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>No permitir asistencia duplicada de la misma persona en la misma actividad y fecha</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 4: unicidad persona + actividad + fecha.</t>
+        </is>
+      </c>
+      <c r="F151" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Juan Pérez ya figura presente hoy en Hogar de día.</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="H151" s="7" t="inlineStr">
+        <is>
+          <t>1. Intentar volver a registrar a Juan Pérez en Hogar de día para hoy  →  El sistema no crea un segundo registro y avisa que ya está registrado
+2. Registrar a Juan Pérez en otra actividad del mismo día  →  Se permite (ver SCRUM-57)</t>
+        </is>
+      </c>
+      <c r="I151" s="7" t="inlineStr"/>
+      <c r="J151" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K151" s="7" t="inlineStr"/>
+      <c r="L151" s="7" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>TC-151</t>
+        </is>
+      </c>
+      <c r="B152" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C152" s="7" t="inlineStr">
+        <is>
+          <t>Registro de asistencia diaria (EP-10) (SCRUM-54)</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>Guardar la asistencia genera la agenda de medicamentos del día</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 5: al guardar la asistencia se activa la generación de la agenda para esa fecha.</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Una persona con esquema de medicación activo.</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="H152" s="7" t="inlineStr">
+        <is>
+          <t>1. Registrar como presente a la persona con medicación y guardar  →  Asistencia guardada
+2. Abrir la agenda diaria de medicamentos  →  Aparecen las tomas de esa persona</t>
+        </is>
+      </c>
+      <c r="I152" s="7" t="inlineStr"/>
+      <c r="J152" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K152" s="7" t="inlineStr"/>
+      <c r="L152" s="7" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>TC-152</t>
+        </is>
+      </c>
+      <c r="B153" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C153" s="7" t="inlineStr">
+        <is>
+          <t>Registro de asistencia diaria (EP-10) (SCRUM-54)</t>
+        </is>
+      </c>
+      <c r="D153" s="7" t="inlineStr">
+        <is>
+          <t>Modificar la asistencia de un día cerrado exige ser Referente y una justificación</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 6: solo un Referente puede corregir un día cerrado y debe justificarlo.</t>
+        </is>
+      </c>
+      <c r="F153" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Existe un día cerrado con asistencia cargada.</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="H153" s="7" t="inlineStr">
+        <is>
+          <t>1. Ingresar como Referente, abrir el día cerrado y editar la asistencia  →  El sistema exige la justificación y no guarda
+2. Repetir con una justificación  →  Se guarda el cambio y queda auditado (quién, cuándo, motivo)
+3. Ingresar como Directora y repetir la edición  →  El sistema lo rechaza por permisos</t>
+        </is>
+      </c>
+      <c r="I153" s="7" t="inlineStr"/>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K153" s="7" t="inlineStr"/>
+      <c r="L153" s="7" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>TC-153</t>
+        </is>
+      </c>
+      <c r="B154" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C154" s="7" t="inlineStr">
+        <is>
+          <t>Historial de asistencia de una persona (EP-10) (SCRUM-55)</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>Ver el historial de asistencia agrupado por actividad desde el perfil</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="inlineStr">
+        <is>
+          <t>Criterios 1 y 5: el historial lista las fechas asistidas por actividad y se ve desde el perfil.</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Una persona con asistencias en distintas actividades.</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-55</t>
+        </is>
+      </c>
+      <c r="H154" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el perfil de la persona y entrar a Asistencia  →  Se muestra el historial
+2. Revisar la agrupación  →  Las fechas aparecen agrupadas por actividad</t>
+        </is>
+      </c>
+      <c r="I154" s="7" t="inlineStr"/>
+      <c r="J154" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K154" s="7" t="inlineStr"/>
+      <c r="L154" s="7" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>TC-154</t>
+        </is>
+      </c>
+      <c r="B155" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C155" s="7" t="inlineStr">
+        <is>
+          <t>Historial de asistencia de una persona (EP-10) (SCRUM-55)</t>
+        </is>
+      </c>
+      <c r="D155" s="7" t="inlineStr">
+        <is>
+          <t>Filtrar el historial por actividad y por rango de fechas</t>
+        </is>
+      </c>
+      <c r="E155" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 2.</t>
+        </is>
+      </c>
+      <c r="F155" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-55</t>
+        </is>
+      </c>
+      <c r="H155" s="7" t="inlineStr">
+        <is>
+          <t>1. Filtrar por una actividad  →  Solo se ven fechas de esa actividad
+2. Agregar un rango de fechas  →  Se acota al rango
+3. Usar un rango invertido  →  El sistema muestra un mensaje de validación</t>
+        </is>
+      </c>
+      <c r="I155" s="7" t="inlineStr"/>
+      <c r="J155" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K155" s="7" t="inlineStr"/>
+      <c r="L155" s="7" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>TC-155</t>
+        </is>
+      </c>
+      <c r="B156" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C156" s="7" t="inlineStr">
+        <is>
+          <t>Historial de asistencia de una persona (EP-10) (SCRUM-55)</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>Mostrar los indicadores: total de días, racha actual y última asistencia</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 3.</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Persona con 5 asistencias, las últimas 3 consecutivas.</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-55</t>
+        </is>
+      </c>
+      <c r="H156" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el historial  →  Total de días = 5, racha actual = 3, última asistencia = fecha más reciente</t>
+        </is>
+      </c>
+      <c r="I156" s="7" t="inlineStr"/>
+      <c r="J156" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K156" s="7" t="inlineStr"/>
+      <c r="L156" s="7" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>TC-156</t>
+        </is>
+      </c>
+      <c r="B157" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C157" s="7" t="inlineStr">
+        <is>
+          <t>Historial de asistencia de una persona (EP-10) (SCRUM-55)</t>
+        </is>
+      </c>
+      <c r="D157" s="7" t="inlineStr">
+        <is>
+          <t>Indicar visualmente a la persona con más de 7 días sin asistir</t>
+        </is>
+      </c>
+      <c r="E157" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 4.</t>
+        </is>
+      </c>
+      <c r="F157" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Persona cuya última asistencia fue hace 8 días y otra hace 6 días.</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-55</t>
+        </is>
+      </c>
+      <c r="H157" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el perfil de la persona con 8 días sin asistir  →  Se muestra el aviso de inasistencia
+2. Abrir el perfil de la persona con 6 días  →  No se muestra el aviso</t>
+        </is>
+      </c>
+      <c r="I157" s="7" t="inlineStr"/>
+      <c r="J157" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K157" s="7" t="inlineStr"/>
+      <c r="L157" s="7" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="7" t="inlineStr">
+        <is>
+          <t>TC-157</t>
+        </is>
+      </c>
+      <c r="B158" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C158" s="7" t="inlineStr">
+        <is>
+          <t>Historial de asistencia de una persona (EP-10) (SCRUM-55)</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>La Directora de Casona solo ve el historial de residentes de Casona</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 6.</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-55</t>
+        </is>
+      </c>
+      <c r="H158" s="7" t="inlineStr">
+        <is>
+          <t>1. Ingresar como Directora y abrir el historial de un residente de Casona  →  Se muestra el historial
+2. Intentar abrir el historial de una persona que no es de Casona  →  El sistema niega el acceso o no lo muestra</t>
+        </is>
+      </c>
+      <c r="I158" s="7" t="inlineStr"/>
+      <c r="J158" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K158" s="7" t="inlineStr"/>
+      <c r="L158" s="7" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="7" t="inlineStr">
+        <is>
+          <t>TC-158</t>
+        </is>
+      </c>
+      <c r="B159" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C159" s="7" t="inlineStr">
+        <is>
+          <t>Estadísticas de asistencia (EP-10) (SCRUM-56)</t>
+        </is>
+      </c>
+      <c r="D159" s="7" t="inlineStr">
+        <is>
+          <t>Ver las estadísticas generales de asistencia</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 1: promedio diario semanal/mensual, asistencia por actividad y comparativa.</t>
+        </is>
+      </c>
+      <c r="F159" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Asistencias cargadas durante al menos 4 semanas.</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-56</t>
+        </is>
+      </c>
+      <c r="H159" s="7" t="inlineStr">
+        <is>
+          <t>1. Ingresar como Referente y abrir Estadísticas de asistencia  →  Se muestran personas por día (promedio semanal y mensual), asistencia por actividad y la comparativa entre actividades
+2. Revisar el formato  →  Los datos se ven en barras o números destacados</t>
+        </is>
+      </c>
+      <c r="I159" s="7" t="inlineStr"/>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K159" s="7" t="inlineStr"/>
+      <c r="L159" s="7" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="7" t="inlineStr">
+        <is>
+          <t>TC-159</t>
+        </is>
+      </c>
+      <c r="B160" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C160" s="7" t="inlineStr">
+        <is>
+          <t>Estadísticas de asistencia (EP-10) (SCRUM-56)</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>Filtrar las estadísticas por rango de fechas y actividad</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 2.</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-56</t>
+        </is>
+      </c>
+      <c r="H160" s="7" t="inlineStr">
+        <is>
+          <t>1. Aplicar un rango de fechas  →  Los números se recalculan para el rango
+2. Aplicar el filtro de actividad  →  Solo cuenta esa actividad</t>
+        </is>
+      </c>
+      <c r="I160" s="7" t="inlineStr"/>
+      <c r="J160" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K160" s="7" t="inlineStr"/>
+      <c r="L160" s="7" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="7" t="inlineStr">
+        <is>
+          <t>TC-160</t>
+        </is>
+      </c>
+      <c r="B161" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C161" s="7" t="inlineStr">
+        <is>
+          <t>Estadísticas de asistencia (EP-10) (SCRUM-56)</t>
+        </is>
+      </c>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>Identificar personas que dejaron de asistir hace más de 14 días</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 3.</t>
+        </is>
+      </c>
+      <c r="F161" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Una persona con última asistencia hace 15 días y otra hace 13.</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-56</t>
+        </is>
+      </c>
+      <c r="H161" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir la sección de inactividad  →  Aparece solo la persona con más de 14 días sin asistir</t>
+        </is>
+      </c>
+      <c r="I161" s="7" t="inlineStr"/>
+      <c r="J161" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K161" s="7" t="inlineStr"/>
+      <c r="L161" s="7" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t>TC-161</t>
+        </is>
+      </c>
+      <c r="B162" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C162" s="7" t="inlineStr">
+        <is>
+          <t>Estadísticas de asistencia (EP-10) (SCRUM-56)</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>Las estadísticas son accesibles solo para Referentes</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 5.</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-56</t>
+        </is>
+      </c>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
+          <t>1. Ingresar como Directora, Coordinador y Escucha e intentar abrir Estadísticas  →  No se muestra la opción y el acceso por URL se rechaza</t>
+        </is>
+      </c>
+      <c r="I162" s="7" t="inlineStr"/>
+      <c r="J162" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K162" s="7" t="inlineStr"/>
+      <c r="L162" s="7" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="7" t="inlineStr">
+        <is>
+          <t>TC-162</t>
+        </is>
+      </c>
+      <c r="B163" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C163" s="7" t="inlineStr">
+        <is>
+          <t>Estadísticas de asistencia (EP-10) (SCRUM-56)</t>
+        </is>
+      </c>
+      <c r="D163" s="7" t="inlineStr">
+        <is>
+          <t>Exportar el resumen mensual de asistencia a PDF</t>
+        </is>
+      </c>
+      <c r="E163" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 6.</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-56</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>1. Elegir un mes y exportar a PDF  →  Se descarga un PDF con el resumen del mes
+2. Exportar un mes sin datos  →  El sistema avisa que no hay datos o genera el PDF vacío sin error</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="inlineStr"/>
+      <c r="J163" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K163" s="7" t="inlineStr"/>
+      <c r="L163" s="7" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="7" t="inlineStr">
+        <is>
+          <t>TC-163</t>
+        </is>
+      </c>
+      <c r="B164" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C164" s="7" t="inlineStr">
+        <is>
+          <t>Asistencia por actividad (EP-10) (SCRUM-57)</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>Las actividades recurrentes del calendario aparecen en el registro de asistencia</t>
+        </is>
+      </c>
+      <c r="E164" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 1: merendero y grupos se sincronizan desde el calendario.</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Un evento recurrente "Merendero" en el calendario general.</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-57</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el registro de asistencia de un día en que corresponde el merendero  →  El merendero está disponible como actividad
+2. Crear un grupo recurrente nuevo en el calendario y volver al registro  →  El grupo aparece sin cargarlo a mano</t>
+        </is>
+      </c>
+      <c r="I164" s="7" t="inlineStr"/>
+      <c r="J164" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K164" s="7" t="inlineStr"/>
+      <c r="L164" s="7" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="7" t="inlineStr">
+        <is>
+          <t>TC-164</t>
+        </is>
+      </c>
+      <c r="B165" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C165" s="7" t="inlineStr">
+        <is>
+          <t>Asistencia por actividad (EP-10) (SCRUM-57)</t>
+        </is>
+      </c>
+      <c r="D165" s="7" t="inlineStr">
+        <is>
+          <t>Registrar a la misma persona en varias actividades del mismo día</t>
+        </is>
+      </c>
+      <c r="E165" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 2.</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-57</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>1. Marcar a una persona en Hogar de día y en Merendero el mismo día  →  Ambos registros se guardan</t>
+        </is>
+      </c>
+      <c r="I165" s="7" t="inlineStr"/>
+      <c r="J165" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K165" s="7" t="inlineStr"/>
+      <c r="L165" s="7" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>TC-165</t>
+        </is>
+      </c>
+      <c r="B166" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C166" s="7" t="inlineStr">
+        <is>
+          <t>Asistencia por actividad (EP-10) (SCRUM-57)</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>Los referentes configuran las actividades disponibles</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 3.</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-57</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>1. Como Referente, agregar, editar y desactivar una actividad  →  Los cambios se reflejan en el registro de asistencia
+2. Intentarlo como Escucha  →  El sistema lo rechaza</t>
+        </is>
+      </c>
+      <c r="I166" s="7" t="inlineStr"/>
+      <c r="J166" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K166" s="7" t="inlineStr"/>
+      <c r="L166" s="7" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="7" t="inlineStr">
+        <is>
+          <t>TC-166</t>
+        </is>
+      </c>
+      <c r="B167" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C167" s="7" t="inlineStr">
+        <is>
+          <t>Asistencia por actividad (EP-10) (SCRUM-57)</t>
+        </is>
+      </c>
+      <c r="D167" s="7" t="inlineStr">
+        <is>
+          <t>La asistencia de la Casona es diaria y separada del Hogar de día</t>
+        </is>
+      </c>
+      <c r="E167" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 4.</t>
+        </is>
+      </c>
+      <c r="F167" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-57</t>
+        </is>
+      </c>
+      <c r="H167" s="7" t="inlineStr">
+        <is>
+          <t>1. Registrar asistencia de Casona y de Hogar de día para el mismo día  →  Cada registro queda separado y las estadísticas no los mezclan</t>
+        </is>
+      </c>
+      <c r="I167" s="7" t="inlineStr"/>
+      <c r="J167" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K167" s="7" t="inlineStr"/>
+      <c r="L167" s="7" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="7" t="inlineStr">
+        <is>
+          <t>TC-167</t>
+        </is>
+      </c>
+      <c r="B168" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C168" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación (Medicación) (SCRUM-59)</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>Cargar un medicamento del catálogo con dosis y hora</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="inlineStr">
+        <is>
+          <t>Criterios 1 y 3.</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Persona con evaluación psiquiátrica vigente; catálogo con Risperdal.</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H168" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el esquema de medicación de la persona y agregar un medicamento  →  El esquema se guarda con medicamento, dosis, hora y fecha de carga</t>
+        </is>
+      </c>
+      <c r="I168" s="7" t="inlineStr"/>
+      <c r="J168" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K168" s="7" t="inlineStr"/>
+      <c r="L168" s="7" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="7" t="inlineStr">
+        <is>
+          <t>TC-168</t>
+        </is>
+      </c>
+      <c r="B169" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C169" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación (Medicación) (SCRUM-59)</t>
+        </is>
+      </c>
+      <c r="D169" s="7" t="inlineStr">
+        <is>
+          <t>No permitir medicamentos fuera del catálogo</t>
+        </is>
+      </c>
+      <c r="E169" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 1.</t>
+        </is>
+      </c>
+      <c r="F169" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H169" s="7" t="inlineStr">
+        <is>
+          <t>1. Intentar cargar un medicamento que no está en el catálogo  →  El sistema solo permite elegir del catálogo</t>
+        </is>
+      </c>
+      <c r="I169" s="7" t="inlineStr"/>
+      <c r="J169" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K169" s="7" t="inlineStr"/>
+      <c r="L169" s="7" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="7" t="inlineStr">
+        <is>
+          <t>TC-169</t>
+        </is>
+      </c>
+      <c r="B170" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C170" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación (Medicación) (SCRUM-59)</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>Bloquear la carga sin evaluación psiquiátrica vigente</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 2.</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Persona sin evaluación psiquiátrica.</t>
+        </is>
+      </c>
+      <c r="G170" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H170" s="7" t="inlineStr">
+        <is>
+          <t>1. Intentar agregar un medicamento  →  El sistema bloquea la carga e indica el motivo</t>
+        </is>
+      </c>
+      <c r="I170" s="7" t="inlineStr"/>
+      <c r="J170" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K170" s="7" t="inlineStr"/>
+      <c r="L170" s="7" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="7" t="inlineStr">
+        <is>
+          <t>TC-170</t>
+        </is>
+      </c>
+      <c r="B171" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C171" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación (Medicación) (SCRUM-59)</t>
+        </is>
+      </c>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>Stock en 0: alertar y marcar el medicamento como pendiente de stock</t>
+        </is>
+      </c>
+      <c r="E171" s="7" t="inlineStr">
+        <is>
+          <t>Criterios 5 y 6.</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Medicamento con stock 0 en farmacia.</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>1. Cargar el esquema con ese medicamento  →  Se muestra la alerta, se permite guardar y el medicamento queda marcado como pendiente de stock
+2. Abrir la agenda diaria  →  Ese medicamento no se incluye como toma disponible</t>
+        </is>
+      </c>
+      <c r="I171" s="7" t="inlineStr"/>
+      <c r="J171" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K171" s="7" t="inlineStr"/>
+      <c r="L171" s="7" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="7" t="inlineStr">
+        <is>
+          <t>TC-171</t>
+        </is>
+      </c>
+      <c r="B172" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C172" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación (Medicación) (SCRUM-59)</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>Registrar quién cargó el esquema y cuándo</t>
+        </is>
+      </c>
+      <c r="E172" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 7.</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>1. Cargar un medicamento y consultar el detalle o la auditoría  →  Figuran el usuario y la fecha y hora de la carga</t>
+        </is>
+      </c>
+      <c r="I172" s="7" t="inlineStr"/>
+      <c r="J172" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K172" s="7" t="inlineStr"/>
+      <c r="L172" s="7" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>TC-172</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación (Medicación) (SCRUM-59)</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>Visibilidad del esquema según el rol</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 8: visible para Referente, Directora y Coordinador; no para Escucha.</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Persona con esquema cargado.</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el esquema como Referente, Directora y Coordinador  →  Se ve en los tres casos
+2. Abrirlo como Escucha  →  No se muestra la sección y el acceso por API responde 403</t>
+        </is>
+      </c>
+      <c r="I173" s="7" t="inlineStr"/>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K173" s="7" t="inlineStr"/>
+      <c r="L173" s="7" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="7" t="inlineStr">
+        <is>
+          <t>TC-173</t>
+        </is>
+      </c>
+      <c r="B174" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C174" s="7" t="inlineStr">
+        <is>
+          <t>Agenda diaria de medicamentos (Medicación) (SCRUM-60)</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>La agenda se genera al registrar la asistencia y agrupa las tomas por hora</t>
+        </is>
+      </c>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>Criterios 1 y 2.</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Juan Pérez (Risperdal 2 mg 08:00) y José Reyes (Vitamina D 500 mg 08:00) presentes hoy.</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-60</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir la agenda diaria  →  Bajo 08:00 figuran Juan Pérez: Risperdal 2mg y José Reyes: Vitamina D 500mg</t>
+        </is>
+      </c>
+      <c r="I174" s="7" t="inlineStr"/>
+      <c r="J174" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K174" s="7" t="inlineStr"/>
+      <c r="L174" s="7" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
+        <is>
+          <t>TC-174</t>
+        </is>
+      </c>
+      <c r="B175" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>Agenda diaria de medicamentos (Medicación) (SCRUM-60)</t>
+        </is>
+      </c>
+      <c r="D175" s="7" t="inlineStr">
+        <is>
+          <t>Solo aparecen las personas presentes con medicación cargada</t>
+        </is>
+      </c>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 3.</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Una persona con medicación que no asistió hoy y otra presente sin medicación.</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-60</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir la agenda de hoy  →  No aparece ninguna de las dos</t>
+        </is>
+      </c>
+      <c r="I175" s="7" t="inlineStr"/>
+      <c r="J175" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K175" s="7" t="inlineStr"/>
+      <c r="L175" s="7" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
+        <is>
+          <t>TC-175</t>
+        </is>
+      </c>
+      <c r="B176" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C176" s="7" t="inlineStr">
+        <is>
+          <t>Agenda diaria de medicamentos (Medicación) (SCRUM-60)</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>Marcar una toma como Administrada o No administrada con observación opcional</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 4.</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G176" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-60</t>
+        </is>
+      </c>
+      <c r="H176" s="7" t="inlineStr">
+        <is>
+          <t>1. Marcar una toma como Administrada  →  La toma queda como Administrada con usuario y hora
+2. Marcar otra como No administrada  →  Queda No administrada con la observación</t>
+        </is>
+      </c>
+      <c r="I176" s="7" t="inlineStr"/>
+      <c r="J176" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K176" s="7" t="inlineStr"/>
+      <c r="L176" s="7" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>TC-176</t>
+        </is>
+      </c>
+      <c r="B177" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C177" s="7" t="inlineStr">
+        <is>
+          <t>Agenda diaria de medicamentos (Medicación) (SCRUM-60)</t>
+        </is>
+      </c>
+      <c r="D177" s="7" t="inlineStr">
+        <is>
+          <t>Acceso directo a la agenda del día desde el panel principal</t>
+        </is>
+      </c>
+      <c r="E177" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 5.</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-60</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>1. Ingresar y mirar el panel principal  →  Hay un acceso directo visible a la agenda de hoy que la abre</t>
+        </is>
+      </c>
+      <c r="I177" s="7" t="inlineStr"/>
+      <c r="J177" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K177" s="7" t="inlineStr"/>
+      <c r="L177" s="7" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>TC-177</t>
+        </is>
+      </c>
+      <c r="B178" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C178" s="7" t="inlineStr">
+        <is>
+          <t>Agenda diaria de medicamentos (Medicación) (SCRUM-60)</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>Consultar la agenda de días anteriores</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 6.</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Agenda con tomas administradas ayer.</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-60</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr">
+        <is>
+          <t>1. Elegir la fecha de ayer  →  Se ve la agenda de ese día con el estado de cada toma</t>
+        </is>
+      </c>
+      <c r="I178" s="7" t="inlineStr"/>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K178" s="7" t="inlineStr"/>
+      <c r="L178" s="7" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>TC-178</t>
+        </is>
+      </c>
+      <c r="B179" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C179" s="7" t="inlineStr">
+        <is>
+          <t>Historial de medicación (Medicación) (SCRUM-61)</t>
+        </is>
+      </c>
+      <c r="D179" s="7" t="inlineStr">
+        <is>
+          <t>Ver el historial de tomas desde el perfil de la persona</t>
+        </is>
+      </c>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>Criterios 1 y 4.</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Persona con tomas programadas, administradas y no administradas.</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-61</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el perfil y entrar a la sección Medicación  →  El historial muestra por fecha las tomas programadas, administradas y no administradas</t>
+        </is>
+      </c>
+      <c r="I179" s="7" t="inlineStr"/>
+      <c r="J179" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K179" s="7" t="inlineStr"/>
+      <c r="L179" s="7" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>TC-179</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>Historial de medicación (Medicación) (SCRUM-61)</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>Filtrar por rango de fechas y por medicamento</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 2.</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-61</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
+          <t>1. Aplicar rango de fechas y un medicamento  →  Solo se ven las tomas de ese medicamento en el rango</t>
+        </is>
+      </c>
+      <c r="I180" s="7" t="inlineStr"/>
+      <c r="J180" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K180" s="7" t="inlineStr"/>
+      <c r="L180" s="7" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>TC-180</t>
+        </is>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>Historial de medicación (Medicación) (SCRUM-61)</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>Resaltar las tomas no administradas</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 3.</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-61</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
+          <t>1. Revisar el historial  →  Las tomas No administradas se distinguen visualmente</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="inlineStr"/>
+      <c r="J181" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K181" s="7" t="inlineStr"/>
+      <c r="L181" s="7" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>TC-181</t>
+        </is>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>Historial de medicación (Medicación) (SCRUM-61)</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>Acceso restringido a Referentes y Directora</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 5.</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-61</t>
+        </is>
+      </c>
+      <c r="H182" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el historial como Referente y Directora  →  Se ve
+2. Abrirlo como Escucha  →  No se muestra y la API responde 403
+3. Abrirlo como Coordinador  →  A confirmar: la historia no lo incluye pero SCRUM-59 sí lo deja ver el esquema</t>
+        </is>
+      </c>
+      <c r="I182" s="7" t="inlineStr"/>
+      <c r="J182" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K182" s="7" t="inlineStr"/>
+      <c r="L182" s="7" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
+        <is>
+          <t>TC-182</t>
+        </is>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>Historial de medicación (Medicación) (SCRUM-61)</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>Exportar el historial de medicación a PDF</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 6.</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-61</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="inlineStr">
+        <is>
+          <t>1. Exportar el historial de una persona  →  Se descarga un PDF con las tomas del filtro
+2. Exportar uno sin tomas  →  El sistema avisa o genera el PDF vacío sin error</t>
+        </is>
+      </c>
+      <c r="I183" s="7" t="inlineStr"/>
+      <c r="J183" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K183" s="7" t="inlineStr"/>
+      <c r="L183" s="7" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>TC-183</t>
+        </is>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>Stock de medicamentos (Medicación) (SCRUM-71)</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>Registrar el ingreso de medicamentos</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 1.</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-71</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>1. Cargar un ingreso  →  El stock del medicamento sube 30 y queda un movimiento de ingreso
+2. Cargar un ingreso con cantidad 0 o negativa  →  El sistema muestra un mensaje de validación</t>
+        </is>
+      </c>
+      <c r="I184" s="7" t="inlineStr"/>
+      <c r="J184" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K184" s="7" t="inlineStr"/>
+      <c r="L184" s="7" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
+        <is>
+          <t>TC-184</t>
+        </is>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>Stock de medicamentos (Medicación) (SCRUM-71)</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>Descontar el stock al marcar una toma como administrada</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 2.</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Stock de Risperdal = 10 y una toma en la agenda.</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-71</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>1. Marcar la toma como Administrada  →  El stock baja y queda un movimiento de consumo
+2. Marcarla como No administrada  →  El stock no cambia</t>
+        </is>
+      </c>
+      <c r="I185" s="7" t="inlineStr"/>
+      <c r="J185" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K185" s="7" t="inlineStr"/>
+      <c r="L185" s="7" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="inlineStr">
+        <is>
+          <t>TC-185</t>
+        </is>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>Stock de medicamentos (Medicación) (SCRUM-71)</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>Alertar cuando el stock está por debajo del umbral configurable</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 3.</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-71</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>1. Configurar el umbral de un medicamento  →  Se guarda el umbral de ese medicamento
+2. Dejar el stock por debajo del umbral  →  Se muestra la alerta de stock bajo</t>
+        </is>
+      </c>
+      <c r="I186" s="7" t="inlineStr"/>
+      <c r="J186" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K186" s="7" t="inlineStr"/>
+      <c r="L186" s="7" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>TC-186</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>Stock de medicamentos (Medicación) (SCRUM-71)</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>Ver el historial de movimientos de un medicamento</t>
+        </is>
+      </c>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 4.</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-71</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el historial de un medicamento con ingresos y consumos  →  Lista cada ingreso y consumo con su fecha</t>
+        </is>
+      </c>
+      <c r="I187" s="7" t="inlineStr"/>
+      <c r="J187" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K187" s="7" t="inlineStr"/>
+      <c r="L187" s="7" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t>TC-187</t>
+        </is>
+      </c>
+      <c r="B188" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C188" s="7" t="inlineStr">
+        <is>
+          <t>Stock de medicamentos (Medicación) (SCRUM-71)</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>Permisos de gestión del stock</t>
+        </is>
+      </c>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 5.</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-71</t>
+        </is>
+      </c>
+      <c r="H188" s="7" t="inlineStr">
+        <is>
+          <t>1. Gestionar el stock como Referente y Directora  →  Se permite
+2. Intentarlo como Escucha y Coordinador  →  No se permite (confirmar el caso del Coordinador)</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="inlineStr"/>
+      <c r="J188" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K188" s="7" t="inlineStr"/>
+      <c r="L188" s="7" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
+        <is>
+          <t>TC-188</t>
+        </is>
+      </c>
+      <c r="B189" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C189" s="7" t="inlineStr">
+        <is>
+          <t>Stock de medicamentos (Medicación) (SCRUM-71)</t>
+        </is>
+      </c>
+      <c r="D189" s="7" t="inlineStr">
+        <is>
+          <t>El stock de medicamentos es independiente del stock de ropa</t>
+        </is>
+      </c>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 6.</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Módulo de stock de ropa, si existe.</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-71</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="inlineStr">
+        <is>
+          <t>1. Mover stock de medicamentos y mirar el de ropa  →  El stock de ropa no cambia y viceversa</t>
+        </is>
+      </c>
+      <c r="I189" s="7" t="inlineStr"/>
+      <c r="J189" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K189" s="7" t="inlineStr"/>
+      <c r="L189" s="7" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr">
+        <is>
+          <t>TC-189</t>
+        </is>
+      </c>
+      <c r="B190" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C190" s="7" t="inlineStr">
+        <is>
+          <t>Revisión mensual del esquema (Medicación) (SCRUM-75)</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>Un medicamento nuevo queda activo y el desactivado se conserva como historial</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="inlineStr">
+        <is>
+          <t>Criterios 1, 2 y 3.</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="inlineStr">
+        <is>
+          <t>1. Cargar un medicamento nuevo  →  Queda activo
+2. Desactivarlo  →  Pasa a inactivo pero el registro se conserva</t>
+        </is>
+      </c>
+      <c r="I190" s="7" t="inlineStr"/>
+      <c r="J190" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K190" s="7" t="inlineStr"/>
+      <c r="L190" s="7" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="7" t="inlineStr">
+        <is>
+          <t>TC-190</t>
+        </is>
+      </c>
+      <c r="B191" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C191" s="7" t="inlineStr">
+        <is>
+          <t>Revisión mensual del esquema (Medicación) (SCRUM-75)</t>
+        </is>
+      </c>
+      <c r="D191" s="7" t="inlineStr">
+        <is>
+          <t>La agenda diaria muestra solo los esquemas activos</t>
+        </is>
+      </c>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 4.</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Una persona con un esquema activo y otro inactivo.</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir la agenda del día  →  Solo aparece el esquema activo</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="inlineStr"/>
+      <c r="J191" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K191" s="7" t="inlineStr"/>
+      <c r="L191" s="7" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
+        <is>
+          <t>TC-191</t>
+        </is>
+      </c>
+      <c r="B192" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C192" s="7" t="inlineStr">
+        <is>
+          <t>Revisión mensual del esquema (Medicación) (SCRUM-75)</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>Los esquemas anteriores son visibles desde el perfil</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 5.</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir el perfil y ver Medicación  →  Hay una sección o filtro con los esquemas inactivos</t>
+        </is>
+      </c>
+      <c r="I192" s="7" t="inlineStr"/>
+      <c r="J192" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K192" s="7" t="inlineStr"/>
+      <c r="L192" s="7" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>TC-192</t>
+        </is>
+      </c>
+      <c r="B193" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C193" s="7" t="inlineStr">
+        <is>
+          <t>Revisión mensual del esquema (Medicación) (SCRUM-75)</t>
+        </is>
+      </c>
+      <c r="D193" s="7" t="inlineStr">
+        <is>
+          <t>Alertar cuando un esquema lleva más de 30 días sin revisión</t>
+        </is>
+      </c>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 6.</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Esquema con revisado_en de hace 31 días y otro de hace 29.</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="inlineStr">
+        <is>
+          <t>1. Abrir los esquemas  →  Se alerta solo el de 31 días</t>
+        </is>
+      </c>
+      <c r="I193" s="7" t="inlineStr"/>
+      <c r="J193" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K193" s="7" t="inlineStr"/>
+      <c r="L193" s="7" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>TC-193</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>Revisión mensual del esquema (Medicación) (SCRUM-75)</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>Bloquear nuevos medicamentos con la evaluación psiquiátrica vencida</t>
+        </is>
+      </c>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 7: más de 6 meses.</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos. Evaluación de hace 6 meses y 1 día, y otra de hace 5 meses.</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>1. Intentar agregar un medicamento a la persona con evaluación vencida  →  Se bloquea con un mensaje
+2. Hacerlo con la evaluación vigente  →  Se permite</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="inlineStr"/>
+      <c r="J194" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K194" s="7" t="inlineStr"/>
+      <c r="L194" s="7" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
+        <is>
+          <t>TC-194</t>
+        </is>
+      </c>
+      <c r="B195" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C195" s="7" t="inlineStr">
+        <is>
+          <t>Revisión mensual del esquema (Medicación) (SCRUM-75)</t>
+        </is>
+      </c>
+      <c r="D195" s="7" t="inlineStr">
+        <is>
+          <t>Revisar el esquema registra la fecha y el usuario</t>
+        </is>
+      </c>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
+          <t>Criterio 8.</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado; usuarios de prueba *@test.com con los roles Referente, Directora, Coordinador y Escucha; sesión iniciada con el rol indicado en los pasos.</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-75</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>1. Marcar el esquema como revisado  →  Se guardan revisado_en (ahora) y revisado_por (usuario actual) y desaparece la alerta de 30 días</t>
+        </is>
+      </c>
+      <c r="I195" s="7" t="inlineStr"/>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="K195" s="7" t="inlineStr"/>
+      <c r="L195" s="7" t="inlineStr"/>
+      <c r="M195" s="7" t="inlineStr">
+        <is>
+          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M147"/>
+  <autoFilter ref="A1:M195"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J195" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,OK,Falla,Bloqueado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12390,7 +15107,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -12452,7 +15169,7 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -12514,7 +15231,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -12577,7 +15294,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -12639,7 +15356,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -12701,7 +15418,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -12764,7 +15481,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -12826,7 +15543,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -12889,7 +15606,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -12951,7 +15668,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -13013,7 +15730,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -13075,7 +15792,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -13138,7 +15855,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -13200,7 +15917,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -13262,7 +15979,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -13325,7 +16042,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -13388,7 +16105,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -13451,7 +16168,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -13514,7 +16231,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -13577,7 +16294,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -13639,7 +16356,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -13701,7 +16418,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -13764,7 +16481,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -13827,7 +16544,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -13890,7 +16607,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -13952,7 +16669,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -14015,7 +16732,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -14078,7 +16795,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -14140,7 +16857,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -14202,7 +16919,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -14265,7 +16982,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -14328,7 +17045,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -14391,7 +17108,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -14454,7 +17171,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -14516,7 +17233,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -14579,7 +17296,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -14641,7 +17358,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -14704,7 +17421,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -14767,7 +17484,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -14830,7 +17547,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -14892,7 +17609,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -14955,7 +17672,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -15018,7 +17735,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -15081,7 +17798,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -15143,7 +17860,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -15206,7 +17923,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -15268,7 +17985,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -15330,7 +18047,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -15392,7 +18109,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -15454,7 +18171,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -15516,7 +18233,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -15578,7 +18295,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -15640,7 +18357,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -15702,7 +18419,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -15764,7 +18481,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -15826,7 +18543,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -15888,7 +18605,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -15950,7 +18667,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -16012,7 +18729,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -16075,7 +18792,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -16138,7 +18855,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -16201,7 +18918,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -16264,7 +18981,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -16327,7 +19044,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -16389,7 +19106,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -16451,7 +19168,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -16513,7 +19230,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -16575,7 +19292,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -16637,7 +19354,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -16699,7 +19416,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -16762,7 +19479,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -16825,7 +19542,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -16888,7 +19605,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -16951,7 +19668,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -17013,7 +19730,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -17076,7 +19793,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -17138,7 +19855,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -17200,7 +19917,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -17263,7 +19980,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -17325,7 +20042,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -17388,7 +20105,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -17450,7 +20167,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -17512,7 +20229,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -17574,7 +20291,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -17636,7 +20353,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -17698,7 +20415,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -17760,7 +20477,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -17822,7 +20539,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -17884,7 +20601,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -17947,7 +20664,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -18009,7 +20726,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -18072,7 +20789,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -18135,7 +20852,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -18198,7 +20915,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -18261,7 +20978,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -18323,7 +21040,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -18385,7 +21102,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -18447,7 +21164,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -18509,7 +21226,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -18572,7 +21289,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -18635,7 +21352,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -18698,7 +21415,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -18761,7 +21478,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -18823,7 +21540,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -18885,7 +21602,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -18947,7 +21664,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -19009,7 +21726,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -19072,7 +21789,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -19134,7 +21851,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -19196,7 +21913,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -19259,7 +21976,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -19322,7 +22039,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -19384,7 +22101,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -19446,7 +22163,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -19508,7 +22225,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -19571,7 +22288,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -19633,7 +22350,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -19695,7 +22412,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -19757,7 +22474,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -19819,7 +22536,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -19881,7 +22598,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -19943,7 +22660,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -20005,7 +22722,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -20067,7 +22784,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -20129,7 +22846,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -20191,7 +22908,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -20253,7 +22970,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -20315,7 +23032,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -20378,7 +23095,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -20441,7 +23158,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -20503,7 +23220,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -20565,7 +23282,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -20627,7 +23344,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -20690,7 +23407,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -20753,7 +23470,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -20815,7 +23532,7 @@
       </c>
       <c r="K137" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L137" s="7" t="inlineStr">
@@ -20877,7 +23594,7 @@
       </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L138" s="7" t="inlineStr">
@@ -20939,7 +23656,7 @@
       </c>
       <c r="K139" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L139" s="7" t="inlineStr">
@@ -21002,7 +23719,7 @@
       </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L140" s="7" t="inlineStr">
@@ -21065,7 +23782,7 @@
       </c>
       <c r="K141" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L141" s="7" t="inlineStr">
@@ -21127,7 +23844,7 @@
       </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L142" s="7" t="inlineStr">
@@ -21189,7 +23906,7 @@
       </c>
       <c r="K143" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L143" s="7" t="inlineStr">
@@ -21252,7 +23969,7 @@
       </c>
       <c r="K144" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L144" s="7" t="inlineStr">
@@ -21314,7 +24031,7 @@
       </c>
       <c r="K145" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L145" s="7" t="inlineStr">
@@ -21376,7 +24093,7 @@
       </c>
       <c r="K146" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L146" s="7" t="inlineStr">
@@ -21439,7 +24156,7 @@
       </c>
       <c r="K147" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L147" s="7" t="inlineStr">
@@ -21501,7 +24218,7 @@
       </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L148" s="7" t="inlineStr">
@@ -21563,7 +24280,7 @@
       </c>
       <c r="K149" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L149" s="7" t="inlineStr">
@@ -21625,7 +24342,7 @@
       </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L150" s="7" t="inlineStr">
@@ -21687,7 +24404,7 @@
       </c>
       <c r="K151" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L151" s="7" t="inlineStr">
@@ -21749,7 +24466,7 @@
       </c>
       <c r="K152" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L152" s="7" t="inlineStr">
@@ -21812,7 +24529,7 @@
       </c>
       <c r="K153" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L153" s="7" t="inlineStr">
@@ -21874,7 +24591,7 @@
       </c>
       <c r="K154" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L154" s="7" t="inlineStr">
@@ -21936,7 +24653,7 @@
       </c>
       <c r="K155" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L155" s="7" t="inlineStr">
@@ -21998,7 +24715,7 @@
       </c>
       <c r="K156" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L156" s="7" t="inlineStr">
@@ -22061,7 +24778,7 @@
       </c>
       <c r="K157" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L157" s="7" t="inlineStr">
@@ -22124,7 +24841,7 @@
       </c>
       <c r="K158" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L158" s="7" t="inlineStr">
@@ -22186,7 +24903,7 @@
       </c>
       <c r="K159" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L159" s="7" t="inlineStr">
@@ -22248,7 +24965,7 @@
       </c>
       <c r="K160" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L160" s="7" t="inlineStr">
@@ -22310,7 +25027,7 @@
       </c>
       <c r="K161" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L161" s="7" t="inlineStr">
@@ -22373,7 +25090,7 @@
       </c>
       <c r="K162" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L162" s="7" t="inlineStr">
@@ -22435,7 +25152,7 @@
       </c>
       <c r="K163" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L163" s="7" t="inlineStr">
@@ -22497,7 +25214,7 @@
       </c>
       <c r="K164" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L164" s="7" t="inlineStr">
@@ -22559,7 +25276,7 @@
       </c>
       <c r="K165" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L165" s="7" t="inlineStr">
@@ -22621,7 +25338,7 @@
       </c>
       <c r="K166" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L166" s="7" t="inlineStr">
@@ -22683,7 +25400,7 @@
       </c>
       <c r="K167" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L167" s="7" t="inlineStr">
@@ -22745,7 +25462,7 @@
       </c>
       <c r="K168" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L168" s="7" t="inlineStr">
@@ -22807,7 +25524,7 @@
       </c>
       <c r="K169" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L169" s="7" t="inlineStr">
@@ -22869,7 +25586,7 @@
       </c>
       <c r="K170" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L170" s="7" t="inlineStr">
@@ -22932,7 +25649,7 @@
       </c>
       <c r="K171" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L171" s="7" t="inlineStr">
@@ -22995,7 +25712,7 @@
       </c>
       <c r="K172" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L172" s="7" t="inlineStr">
@@ -23057,7 +25774,7 @@
       </c>
       <c r="K173" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L173" s="7" t="inlineStr">
@@ -23119,7 +25836,7 @@
       </c>
       <c r="K174" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L174" s="7" t="inlineStr">
@@ -23182,7 +25899,7 @@
       </c>
       <c r="K175" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L175" s="7" t="inlineStr">
@@ -23244,7 +25961,7 @@
       </c>
       <c r="K176" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L176" s="7" t="inlineStr">
@@ -23307,7 +26024,7 @@
       </c>
       <c r="K177" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L177" s="7" t="inlineStr">
@@ -23370,7 +26087,7 @@
       </c>
       <c r="K178" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L178" s="7" t="inlineStr">
@@ -23433,7 +26150,7 @@
       </c>
       <c r="K179" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L179" s="7" t="inlineStr">
@@ -23495,7 +26212,7 @@
       </c>
       <c r="K180" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L180" s="7" t="inlineStr">
@@ -23557,7 +26274,7 @@
       </c>
       <c r="K181" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L181" s="7" t="inlineStr">
@@ -23620,7 +26337,7 @@
       </c>
       <c r="K182" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L182" s="7" t="inlineStr">
@@ -23682,7 +26399,7 @@
       </c>
       <c r="K183" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L183" s="7" t="inlineStr">
@@ -23744,7 +26461,7 @@
       </c>
       <c r="K184" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L184" s="7" t="inlineStr">
@@ -23806,7 +26523,7 @@
       </c>
       <c r="K185" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L185" s="7" t="inlineStr">
@@ -23868,7 +26585,7 @@
       </c>
       <c r="K186" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L186" s="7" t="inlineStr">
@@ -23930,7 +26647,7 @@
       </c>
       <c r="K187" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L187" s="7" t="inlineStr">
@@ -23992,7 +26709,7 @@
       </c>
       <c r="K188" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L188" s="7" t="inlineStr">
@@ -24054,7 +26771,7 @@
       </c>
       <c r="K189" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L189" s="7" t="inlineStr">
@@ -24116,7 +26833,7 @@
       </c>
       <c r="K190" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L190" s="7" t="inlineStr">
@@ -24178,7 +26895,7 @@
       </c>
       <c r="K191" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L191" s="7" t="inlineStr">
@@ -24241,7 +26958,7 @@
       </c>
       <c r="K192" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L192" s="7" t="inlineStr">
@@ -24304,7 +27021,7 @@
       </c>
       <c r="K193" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L193" s="7" t="inlineStr">
@@ -24367,7 +27084,7 @@
       </c>
       <c r="K194" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L194" s="7" t="inlineStr">
@@ -24430,7 +27147,7 @@
       </c>
       <c r="K195" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L195" s="7" t="inlineStr">
@@ -24492,7 +27209,7 @@
       </c>
       <c r="K196" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L196" s="7" t="inlineStr">
@@ -24554,7 +27271,7 @@
       </c>
       <c r="K197" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L197" s="7" t="inlineStr">
@@ -24617,7 +27334,7 @@
       </c>
       <c r="K198" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L198" s="7" t="inlineStr">
@@ -24679,7 +27396,7 @@
       </c>
       <c r="K199" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L199" s="7" t="inlineStr">
@@ -24741,7 +27458,7 @@
       </c>
       <c r="K200" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L200" s="7" t="inlineStr">
@@ -24803,7 +27520,7 @@
       </c>
       <c r="K201" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L201" s="7" t="inlineStr">
@@ -24865,7 +27582,7 @@
       </c>
       <c r="K202" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L202" s="7" t="inlineStr">
@@ -24927,7 +27644,7 @@
       </c>
       <c r="K203" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L203" s="7" t="inlineStr">
@@ -24990,7 +27707,7 @@
       </c>
       <c r="K204" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L204" s="7" t="inlineStr">
@@ -25053,7 +27770,7 @@
       </c>
       <c r="K205" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L205" s="7" t="inlineStr">
@@ -25115,7 +27832,7 @@
       </c>
       <c r="K206" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L206" s="7" t="inlineStr">
@@ -25177,7 +27894,7 @@
       </c>
       <c r="K207" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L207" s="7" t="inlineStr">
@@ -25240,7 +27957,7 @@
       </c>
       <c r="K208" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L208" s="7" t="inlineStr">
@@ -25303,7 +28020,7 @@
       </c>
       <c r="K209" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L209" s="7" t="inlineStr">
@@ -25366,7 +28083,7 @@
       </c>
       <c r="K210" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L210" s="7" t="inlineStr">
@@ -25429,7 +28146,7 @@
       </c>
       <c r="K211" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L211" s="7" t="inlineStr">
@@ -25491,7 +28208,7 @@
       </c>
       <c r="K212" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L212" s="7" t="inlineStr">
@@ -25553,7 +28270,7 @@
       </c>
       <c r="K213" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L213" s="7" t="inlineStr">
@@ -25615,7 +28332,7 @@
       </c>
       <c r="K214" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L214" s="7" t="inlineStr">
@@ -25678,7 +28395,7 @@
       </c>
       <c r="K215" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L215" s="7" t="inlineStr">
@@ -25740,7 +28457,7 @@
       </c>
       <c r="K216" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L216" s="7" t="inlineStr">
@@ -25802,7 +28519,7 @@
       </c>
       <c r="K217" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L217" s="7" t="inlineStr">
@@ -25864,7 +28581,7 @@
       </c>
       <c r="K218" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L218" s="7" t="inlineStr">
@@ -25927,7 +28644,7 @@
       </c>
       <c r="K219" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L219" s="7" t="inlineStr">
@@ -25990,7 +28707,7 @@
       </c>
       <c r="K220" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L220" s="7" t="inlineStr">
@@ -26052,7 +28769,7 @@
       </c>
       <c r="K221" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L221" s="7" t="inlineStr">
@@ -26114,7 +28831,7 @@
       </c>
       <c r="K222" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L222" s="7" t="inlineStr">
@@ -26176,7 +28893,7 @@
       </c>
       <c r="K223" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L223" s="7" t="inlineStr">
@@ -26238,7 +28955,7 @@
       </c>
       <c r="K224" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L224" s="7" t="inlineStr">
@@ -26300,7 +29017,7 @@
       </c>
       <c r="K225" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L225" s="7" t="inlineStr">
@@ -26362,7 +29079,7 @@
       </c>
       <c r="K226" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L226" s="7" t="inlineStr">
@@ -26424,7 +29141,7 @@
       </c>
       <c r="K227" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L227" s="7" t="inlineStr">
@@ -26486,7 +29203,7 @@
       </c>
       <c r="K228" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L228" s="7" t="inlineStr">
@@ -26548,7 +29265,7 @@
       </c>
       <c r="K229" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L229" s="7" t="inlineStr">
@@ -26611,7 +29328,7 @@
       </c>
       <c r="K230" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L230" s="7" t="inlineStr">
@@ -26673,7 +29390,7 @@
       </c>
       <c r="K231" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L231" s="7" t="inlineStr">
@@ -26735,7 +29452,7 @@
       </c>
       <c r="K232" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L232" s="7" t="inlineStr">
@@ -26798,7 +29515,7 @@
       </c>
       <c r="K233" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L233" s="7" t="inlineStr">
@@ -26861,7 +29578,7 @@
       </c>
       <c r="K234" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L234" s="7" t="inlineStr">
@@ -26923,7 +29640,7 @@
       </c>
       <c r="K235" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L235" s="7" t="inlineStr">
@@ -26985,7 +29702,7 @@
       </c>
       <c r="K236" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L236" s="7" t="inlineStr">
@@ -27047,7 +29764,7 @@
       </c>
       <c r="K237" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L237" s="7" t="inlineStr">
@@ -27109,7 +29826,7 @@
       </c>
       <c r="K238" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L238" s="7" t="inlineStr">
@@ -27167,7 +29884,7 @@
       </c>
       <c r="K239" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L239" s="7" t="inlineStr">
@@ -27225,7 +29942,7 @@
       </c>
       <c r="K240" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L240" s="7" t="inlineStr">
@@ -27283,7 +30000,7 @@
       </c>
       <c r="K241" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L241" s="7" t="inlineStr">
@@ -27341,7 +30058,7 @@
       </c>
       <c r="K242" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L242" s="7" t="inlineStr">
@@ -27399,7 +30116,7 @@
       </c>
       <c r="K243" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L243" s="7" t="inlineStr">
@@ -27457,7 +30174,7 @@
       </c>
       <c r="K244" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L244" s="7" t="inlineStr">
@@ -27515,7 +30232,7 @@
       </c>
       <c r="K245" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L245" s="7" t="inlineStr">
@@ -27573,7 +30290,7 @@
       </c>
       <c r="K246" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L246" s="7" t="inlineStr">
@@ -27631,7 +30348,7 @@
       </c>
       <c r="K247" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L247" s="7" t="inlineStr">
@@ -27689,7 +30406,7 @@
       </c>
       <c r="K248" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L248" s="7" t="inlineStr">
@@ -27751,7 +30468,7 @@
       </c>
       <c r="K249" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L249" s="7" t="inlineStr">
@@ -27813,7 +30530,7 @@
       </c>
       <c r="K250" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L250" s="7" t="inlineStr">
@@ -27871,7 +30588,7 @@
       </c>
       <c r="K251" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L251" s="7" t="inlineStr">
@@ -27929,7 +30646,7 @@
       </c>
       <c r="K252" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L252" s="7" t="inlineStr">
@@ -27991,7 +30708,7 @@
       </c>
       <c r="K253" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L253" s="7" t="inlineStr">
@@ -28049,7 +30766,7 @@
       </c>
       <c r="K254" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L254" s="7" t="inlineStr">
@@ -28107,7 +30824,7 @@
       </c>
       <c r="K255" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L255" s="7" t="inlineStr">
@@ -28165,7 +30882,7 @@
       </c>
       <c r="K256" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L256" s="7" t="inlineStr">
@@ -28223,7 +30940,7 @@
       </c>
       <c r="K257" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L257" s="7" t="inlineStr">
@@ -28281,7 +30998,7 @@
       </c>
       <c r="K258" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L258" s="7" t="inlineStr">
@@ -28339,7 +31056,7 @@
       </c>
       <c r="K259" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L259" s="7" t="inlineStr">
@@ -28397,7 +31114,7 @@
       </c>
       <c r="K260" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L260" s="7" t="inlineStr">
@@ -28455,7 +31172,7 @@
       </c>
       <c r="K261" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L261" s="7" t="inlineStr">
@@ -28513,7 +31230,7 @@
       </c>
       <c r="K262" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L262" s="7" t="inlineStr">
@@ -28571,7 +31288,7 @@
       </c>
       <c r="K263" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L263" s="7" t="inlineStr">
@@ -28633,7 +31350,7 @@
       </c>
       <c r="K264" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L264" s="7" t="inlineStr">
@@ -28695,7 +31412,7 @@
       </c>
       <c r="K265" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L265" s="7" t="inlineStr">
@@ -28753,7 +31470,7 @@
       </c>
       <c r="K266" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L266" s="7" t="inlineStr">
@@ -28811,7 +31528,7 @@
       </c>
       <c r="K267" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L267" s="7" t="inlineStr">
@@ -28869,7 +31586,7 @@
       </c>
       <c r="K268" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L268" s="7" t="inlineStr">
@@ -28927,7 +31644,7 @@
       </c>
       <c r="K269" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L269" s="7" t="inlineStr">
@@ -28985,7 +31702,7 @@
       </c>
       <c r="K270" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L270" s="7" t="inlineStr">
@@ -29043,7 +31760,7 @@
       </c>
       <c r="K271" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L271" s="7" t="inlineStr">
@@ -29101,7 +31818,7 @@
       </c>
       <c r="K272" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L272" s="7" t="inlineStr">
@@ -29159,7 +31876,7 @@
       </c>
       <c r="K273" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L273" s="7" t="inlineStr">
@@ -29221,7 +31938,7 @@
       </c>
       <c r="K274" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L274" s="7" t="inlineStr">
@@ -29283,7 +32000,7 @@
       </c>
       <c r="K275" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L275" s="7" t="inlineStr">
@@ -29345,7 +32062,7 @@
       </c>
       <c r="K276" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L276" s="7" t="inlineStr">
@@ -29403,7 +32120,7 @@
       </c>
       <c r="K277" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L277" s="7" t="inlineStr">
@@ -29465,7 +32182,7 @@
       </c>
       <c r="K278" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L278" s="7" t="inlineStr">
@@ -29527,7 +32244,7 @@
       </c>
       <c r="K279" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L279" s="7" t="inlineStr">
@@ -29585,7 +32302,7 @@
       </c>
       <c r="K280" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L280" s="7" t="inlineStr">
@@ -29643,7 +32360,7 @@
       </c>
       <c r="K281" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L281" s="7" t="inlineStr">
@@ -29701,7 +32418,7 @@
       </c>
       <c r="K282" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L282" s="7" t="inlineStr">
@@ -29759,7 +32476,7 @@
       </c>
       <c r="K283" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L283" s="7" t="inlineStr">
@@ -29817,7 +32534,7 @@
       </c>
       <c r="K284" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L284" s="7" t="inlineStr">
@@ -29875,7 +32592,7 @@
       </c>
       <c r="K285" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L285" s="7" t="inlineStr">
@@ -29933,7 +32650,7 @@
       </c>
       <c r="K286" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L286" s="7" t="inlineStr">
@@ -29991,7 +32708,7 @@
       </c>
       <c r="K287" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L287" s="7" t="inlineStr">
@@ -30049,7 +32766,7 @@
       </c>
       <c r="K288" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L288" s="7" t="inlineStr">
@@ -30107,7 +32824,7 @@
       </c>
       <c r="K289" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L289" s="7" t="inlineStr">
@@ -30165,7 +32882,7 @@
       </c>
       <c r="K290" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L290" s="7" t="inlineStr">
@@ -30223,7 +32940,7 @@
       </c>
       <c r="K291" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L291" s="7" t="inlineStr">
@@ -30281,7 +32998,7 @@
       </c>
       <c r="K292" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L292" s="7" t="inlineStr">
@@ -30339,7 +33056,7 @@
       </c>
       <c r="K293" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L293" s="7" t="inlineStr">
@@ -30397,7 +33114,7 @@
       </c>
       <c r="K294" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L294" s="7" t="inlineStr">
@@ -30455,7 +33172,7 @@
       </c>
       <c r="K295" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L295" s="7" t="inlineStr">
@@ -30513,7 +33230,7 @@
       </c>
       <c r="K296" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L296" s="7" t="inlineStr">
@@ -30571,7 +33288,7 @@
       </c>
       <c r="K297" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L297" s="7" t="inlineStr">
@@ -30633,7 +33350,7 @@
       </c>
       <c r="K298" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L298" s="7" t="inlineStr">
@@ -30695,7 +33412,7 @@
       </c>
       <c r="K299" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L299" s="7" t="inlineStr">
@@ -30757,7 +33474,7 @@
       </c>
       <c r="K300" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L300" s="7" t="inlineStr">
@@ -30819,7 +33536,7 @@
       </c>
       <c r="K301" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L301" s="7" t="inlineStr">
@@ -30881,7 +33598,7 @@
       </c>
       <c r="K302" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L302" s="7" t="inlineStr">
@@ -30939,7 +33656,7 @@
       </c>
       <c r="K303" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L303" s="7" t="inlineStr">
@@ -30997,7 +33714,7 @@
       </c>
       <c r="K304" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L304" s="7" t="inlineStr">
@@ -31055,7 +33772,7 @@
       </c>
       <c r="K305" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L305" s="7" t="inlineStr">
@@ -31113,7 +33830,7 @@
       </c>
       <c r="K306" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L306" s="7" t="inlineStr">
@@ -31171,7 +33888,7 @@
       </c>
       <c r="K307" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L307" s="7" t="inlineStr">
@@ -31229,7 +33946,7 @@
       </c>
       <c r="K308" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L308" s="7" t="inlineStr">
@@ -31287,7 +34004,7 @@
       </c>
       <c r="K309" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L309" s="7" t="inlineStr">
@@ -31345,7 +34062,7 @@
       </c>
       <c r="K310" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L310" s="7" t="inlineStr">
@@ -31403,7 +34120,7 @@
       </c>
       <c r="K311" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L311" s="7" t="inlineStr">
@@ -31461,7 +34178,7 @@
       </c>
       <c r="K312" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L312" s="7" t="inlineStr">
@@ -31519,7 +34236,7 @@
       </c>
       <c r="K313" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L313" s="7" t="inlineStr">
@@ -31577,7 +34294,7 @@
       </c>
       <c r="K314" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L314" s="7" t="inlineStr">
@@ -31635,7 +34352,7 @@
       </c>
       <c r="K315" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L315" s="7" t="inlineStr">
@@ -31693,7 +34410,7 @@
       </c>
       <c r="K316" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L316" s="7" t="inlineStr">
@@ -31751,7 +34468,7 @@
       </c>
       <c r="K317" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L317" s="7" t="inlineStr">
@@ -31809,7 +34526,7 @@
       </c>
       <c r="K318" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L318" s="7" t="inlineStr">
@@ -31867,7 +34584,7 @@
       </c>
       <c r="K319" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L319" s="7" t="inlineStr">
@@ -31929,7 +34646,7 @@
       </c>
       <c r="K320" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L320" s="7" t="inlineStr">
@@ -31991,7 +34708,7 @@
       </c>
       <c r="K321" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L321" s="7" t="inlineStr">
@@ -32049,7 +34766,7 @@
       </c>
       <c r="K322" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L322" s="7" t="inlineStr">
@@ -32107,7 +34824,7 @@
       </c>
       <c r="K323" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L323" s="7" t="inlineStr">
@@ -32169,7 +34886,7 @@
       </c>
       <c r="K324" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L324" s="7" t="inlineStr">
@@ -32231,7 +34948,7 @@
       </c>
       <c r="K325" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L325" s="7" t="inlineStr">
@@ -32289,7 +35006,7 @@
       </c>
       <c r="K326" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L326" s="7" t="inlineStr">
@@ -32351,7 +35068,7 @@
       </c>
       <c r="K327" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L327" s="7" t="inlineStr">
@@ -32413,7 +35130,7 @@
       </c>
       <c r="K328" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L328" s="7" t="inlineStr">
@@ -32475,7 +35192,7 @@
       </c>
       <c r="K329" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L329" s="7" t="inlineStr">
@@ -32537,7 +35254,7 @@
       </c>
       <c r="K330" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L330" s="7" t="inlineStr">
@@ -32599,7 +35316,7 @@
       </c>
       <c r="K331" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L331" s="7" t="inlineStr">
@@ -32661,7 +35378,7 @@
       </c>
       <c r="K332" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L332" s="7" t="inlineStr">
@@ -32723,7 +35440,7 @@
       </c>
       <c r="K333" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L333" s="7" t="inlineStr">
@@ -32785,7 +35502,7 @@
       </c>
       <c r="K334" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L334" s="7" t="inlineStr">
@@ -32847,7 +35564,7 @@
       </c>
       <c r="K335" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L335" s="7" t="inlineStr">
@@ -32909,7 +35626,7 @@
       </c>
       <c r="K336" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L336" s="7" t="inlineStr">
@@ -32971,7 +35688,7 @@
       </c>
       <c r="K337" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L337" s="7" t="inlineStr">
@@ -33033,7 +35750,7 @@
       </c>
       <c r="K338" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L338" s="7" t="inlineStr">
@@ -33095,7 +35812,7 @@
       </c>
       <c r="K339" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L339" s="7" t="inlineStr">
@@ -33157,7 +35874,7 @@
       </c>
       <c r="K340" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L340" s="7" t="inlineStr">
@@ -33219,7 +35936,7 @@
       </c>
       <c r="K341" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L341" s="7" t="inlineStr">
@@ -33281,7 +35998,7 @@
       </c>
       <c r="K342" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L342" s="7" t="inlineStr">
@@ -33343,7 +36060,7 @@
       </c>
       <c r="K343" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L343" s="7" t="inlineStr">
@@ -33405,7 +36122,7 @@
       </c>
       <c r="K344" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L344" s="7" t="inlineStr">
@@ -33467,7 +36184,7 @@
       </c>
       <c r="K345" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L345" s="7" t="inlineStr">
@@ -33529,7 +36246,7 @@
       </c>
       <c r="K346" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L346" s="7" t="inlineStr">
@@ -33591,7 +36308,7 @@
       </c>
       <c r="K347" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L347" s="7" t="inlineStr">
@@ -33653,7 +36370,7 @@
       </c>
       <c r="K348" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L348" s="7" t="inlineStr">
@@ -33715,7 +36432,7 @@
       </c>
       <c r="K349" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L349" s="7" t="inlineStr">
@@ -33773,7 +36490,7 @@
       </c>
       <c r="K350" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L350" s="7" t="inlineStr">
@@ -33831,7 +36548,7 @@
       </c>
       <c r="K351" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L351" s="7" t="inlineStr">
@@ -33893,7 +36610,7 @@
       </c>
       <c r="K352" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L352" s="7" t="inlineStr">
@@ -33955,7 +36672,7 @@
       </c>
       <c r="K353" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L353" s="7" t="inlineStr">
@@ -34017,7 +36734,7 @@
       </c>
       <c r="K354" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L354" s="7" t="inlineStr">
@@ -34079,7 +36796,7 @@
       </c>
       <c r="K355" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L355" s="7" t="inlineStr">
@@ -34141,7 +36858,7 @@
       </c>
       <c r="K356" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L356" s="7" t="inlineStr">
@@ -34203,7 +36920,7 @@
       </c>
       <c r="K357" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L357" s="7" t="inlineStr">
@@ -34265,7 +36982,7 @@
       </c>
       <c r="K358" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L358" s="7" t="inlineStr">
@@ -34327,7 +37044,7 @@
       </c>
       <c r="K359" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L359" s="7" t="inlineStr">
@@ -34389,7 +37106,7 @@
       </c>
       <c r="K360" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L360" s="7" t="inlineStr">
@@ -34451,7 +37168,7 @@
       </c>
       <c r="K361" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L361" s="7" t="inlineStr">
@@ -34513,7 +37230,7 @@
       </c>
       <c r="K362" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L362" s="7" t="inlineStr">
@@ -34575,7 +37292,7 @@
       </c>
       <c r="K363" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L363" s="7" t="inlineStr">
@@ -34637,7 +37354,7 @@
       </c>
       <c r="K364" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L364" s="7" t="inlineStr">
@@ -34699,7 +37416,7 @@
       </c>
       <c r="K365" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L365" s="7" t="inlineStr">
@@ -34761,7 +37478,7 @@
       </c>
       <c r="K366" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L366" s="7" t="inlineStr">
@@ -34823,7 +37540,7 @@
       </c>
       <c r="K367" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L367" s="7" t="inlineStr">
@@ -34885,7 +37602,7 @@
       </c>
       <c r="K368" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L368" s="7" t="inlineStr">
@@ -34947,7 +37664,7 @@
       </c>
       <c r="K369" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L369" s="7" t="inlineStr">
@@ -35009,7 +37726,7 @@
       </c>
       <c r="K370" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L370" s="7" t="inlineStr">
@@ -35071,7 +37788,7 @@
       </c>
       <c r="K371" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L371" s="7" t="inlineStr">
@@ -35133,7 +37850,7 @@
       </c>
       <c r="K372" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L372" s="7" t="inlineStr">
@@ -35195,7 +37912,7 @@
       </c>
       <c r="K373" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L373" s="7" t="inlineStr">
@@ -35257,7 +37974,7 @@
       </c>
       <c r="K374" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L374" s="7" t="inlineStr">
@@ -35319,7 +38036,7 @@
       </c>
       <c r="K375" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L375" s="7" t="inlineStr">
@@ -35381,7 +38098,7 @@
       </c>
       <c r="K376" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L376" s="7" t="inlineStr">
@@ -35443,7 +38160,7 @@
       </c>
       <c r="K377" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L377" s="7" t="inlineStr">
@@ -35505,7 +38222,7 @@
       </c>
       <c r="K378" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L378" s="7" t="inlineStr">
@@ -35567,7 +38284,7 @@
       </c>
       <c r="K379" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L379" s="7" t="inlineStr">
@@ -35629,7 +38346,7 @@
       </c>
       <c r="K380" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L380" s="7" t="inlineStr">
@@ -35691,7 +38408,7 @@
       </c>
       <c r="K381" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L381" s="7" t="inlineStr">
@@ -35753,7 +38470,7 @@
       </c>
       <c r="K382" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L382" s="7" t="inlineStr">
@@ -35815,7 +38532,7 @@
       </c>
       <c r="K383" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L383" s="7" t="inlineStr">
@@ -35877,7 +38594,7 @@
       </c>
       <c r="K384" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L384" s="7" t="inlineStr">
@@ -35939,7 +38656,7 @@
       </c>
       <c r="K385" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L385" s="7" t="inlineStr">
@@ -36001,7 +38718,7 @@
       </c>
       <c r="K386" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L386" s="7" t="inlineStr">
@@ -36063,7 +38780,7 @@
       </c>
       <c r="K387" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L387" s="7" t="inlineStr">
@@ -36125,7 +38842,7 @@
       </c>
       <c r="K388" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L388" s="7" t="inlineStr">
@@ -36187,7 +38904,7 @@
       </c>
       <c r="K389" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L389" s="7" t="inlineStr">
@@ -36249,7 +38966,7 @@
       </c>
       <c r="K390" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L390" s="7" t="inlineStr">
@@ -36311,7 +39028,7 @@
       </c>
       <c r="K391" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L391" s="7" t="inlineStr">
@@ -36373,7 +39090,7 @@
       </c>
       <c r="K392" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L392" s="7" t="inlineStr">
@@ -36435,7 +39152,7 @@
       </c>
       <c r="K393" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L393" s="7" t="inlineStr">
@@ -36497,7 +39214,7 @@
       </c>
       <c r="K394" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L394" s="7" t="inlineStr">
@@ -36559,7 +39276,7 @@
       </c>
       <c r="K395" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L395" s="7" t="inlineStr">
@@ -36621,7 +39338,7 @@
       </c>
       <c r="K396" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L396" s="7" t="inlineStr">
@@ -36683,7 +39400,7 @@
       </c>
       <c r="K397" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L397" s="7" t="inlineStr">
@@ -36745,7 +39462,7 @@
       </c>
       <c r="K398" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L398" s="7" t="inlineStr">
@@ -36807,7 +39524,7 @@
       </c>
       <c r="K399" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L399" s="7" t="inlineStr">
@@ -36869,7 +39586,7 @@
       </c>
       <c r="K400" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L400" s="7" t="inlineStr">
@@ -36931,7 +39648,7 @@
       </c>
       <c r="K401" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L401" s="7" t="inlineStr">
@@ -36993,7 +39710,7 @@
       </c>
       <c r="K402" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L402" s="7" t="inlineStr">
@@ -37055,7 +39772,7 @@
       </c>
       <c r="K403" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L403" s="7" t="inlineStr">
@@ -37117,7 +39834,7 @@
       </c>
       <c r="K404" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L404" s="7" t="inlineStr">
@@ -37179,7 +39896,7 @@
       </c>
       <c r="K405" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L405" s="7" t="inlineStr">
@@ -37241,7 +39958,7 @@
       </c>
       <c r="K406" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L406" s="7" t="inlineStr">
@@ -37303,7 +40020,7 @@
       </c>
       <c r="K407" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L407" s="7" t="inlineStr">
@@ -37365,7 +40082,7 @@
       </c>
       <c r="K408" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L408" s="7" t="inlineStr">
@@ -37427,7 +40144,7 @@
       </c>
       <c r="K409" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L409" s="7" t="inlineStr">
@@ -37489,7 +40206,7 @@
       </c>
       <c r="K410" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L410" s="7" t="inlineStr">
@@ -37551,7 +40268,7 @@
       </c>
       <c r="K411" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L411" s="7" t="inlineStr">
@@ -37613,7 +40330,7 @@
       </c>
       <c r="K412" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L412" s="7" t="inlineStr">
@@ -37675,7 +40392,7 @@
       </c>
       <c r="K413" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L413" s="7" t="inlineStr">
@@ -37737,7 +40454,7 @@
       </c>
       <c r="K414" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L414" s="7" t="inlineStr">
@@ -37799,7 +40516,7 @@
       </c>
       <c r="K415" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L415" s="7" t="inlineStr">
@@ -37861,7 +40578,7 @@
       </c>
       <c r="K416" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L416" s="7" t="inlineStr">
@@ -37923,7 +40640,7 @@
       </c>
       <c r="K417" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L417" s="7" t="inlineStr">
@@ -37985,7 +40702,7 @@
       </c>
       <c r="K418" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L418" s="7" t="inlineStr">
@@ -38043,7 +40760,7 @@
       </c>
       <c r="K419" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L419" s="7" t="inlineStr">
@@ -38105,7 +40822,7 @@
       </c>
       <c r="K420" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L420" s="7" t="inlineStr">
@@ -38167,7 +40884,7 @@
       </c>
       <c r="K421" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L421" s="7" t="inlineStr">
@@ -38229,7 +40946,7 @@
       </c>
       <c r="K422" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L422" s="7" t="inlineStr">
@@ -38291,7 +41008,7 @@
       </c>
       <c r="K423" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L423" s="7" t="inlineStr">
@@ -38353,7 +41070,7 @@
       </c>
       <c r="K424" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L424" s="7" t="inlineStr">
@@ -38415,7 +41132,7 @@
       </c>
       <c r="K425" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L425" s="7" t="inlineStr">
@@ -38477,7 +41194,7 @@
       </c>
       <c r="K426" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L426" s="7" t="inlineStr">
@@ -38539,7 +41256,7 @@
       </c>
       <c r="K427" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L427" s="7" t="inlineStr">
@@ -38601,7 +41318,7 @@
       </c>
       <c r="K428" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L428" s="7" t="inlineStr">
@@ -38663,7 +41380,7 @@
       </c>
       <c r="K429" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L429" s="7" t="inlineStr">
@@ -38725,7 +41442,7 @@
       </c>
       <c r="K430" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L430" s="7" t="inlineStr">
@@ -38787,7 +41504,7 @@
       </c>
       <c r="K431" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L431" s="7" t="inlineStr">
@@ -38813,7 +41530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -39162,27 +41879,27 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Defecto</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Las ramas dev-backend y dev-frontend no tienen los cambios de dev.</t>
+          <t>La suite de integración colgaba el equipo: cada clase de test levanta su propio SQL Server en Docker y xUnit las corría en paralelo (hasta 16 contenedores) contra una VM de WSL con tope de 4 GB; Docker se caía y los tests quedaban sin resultado.</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Backend (tests de integración)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Corregido en dev</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Sincronizar por PR antes de que sigan Emir y Belén.</t>
+          <t>AssemblyInfo.cs desactiva el paralelismo y el factory limita cada SQL Server a 1 GB (MSSQL_MEMORY_LIMIT_MB). Resultado: 240 de 240 OK en 10 min 38 s.</t>
         </is>
       </c>
     </row>
@@ -39197,27 +41914,207 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
+          <t>Las ramas dev-backend y dev-frontend no tienen los cambios de dev.</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Git</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Sincronizar por PR antes de que sigan Emir y Belén.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
           <t>Jira: SCRUM-198 y SCRUM-215 (QA) siguen 'En curso'.</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Jira</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Abierta</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Cerrar con el resultado de esta ejecución.</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>El primer criterio dice "Hogar de día, , Casona (diaria)": falta una actividad en el texto. A confirmar cuáles son.</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>No se define cuándo se "cierra" un día (¿automático a medianoche, manual por un Referente?). Necesario para el último criterio.</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Pide actividades configurables por los Referentes pero no hay una historia para esa pantalla de configuración.</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-57</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Los permisos del Coordinador de Casona no son consistentes entre historias (SCRUM-59 lo incluye, SCRUM-60, 61 y 71 no lo nombran).</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59 / 60 / 61 / 71</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59 habla de "stock en farmacia" y SCRUM-71 de "stock del Centro Barrial": confirmar que son el mismo inventario.</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59 / 71</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F13"/>
+  <autoFilter ref="A1:F19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/qa/Plan_de_pruebas_Sprint_1-4.xlsx
+++ b/docs/qa/Plan_de_pruebas_Sprint_1-4.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parte A - Manuales'!$A$1:$M$195</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pasos TC'!$A$1:$E$90</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parte B - Automatizados'!$A$1:$L$431</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defectos y pendientes'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parte B - Automatizados'!$A$1:$L$449</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defectos y pendientes'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Casos manuales (TC) y automatizados (TA) de los Sprint 1 a 4 (el Sprint 4 todavía sin desarrollo: casos Pendientes). Se actualiza con los contadores de las hojas.</t>
+          <t>Casos manuales (TC) y automatizados (TA) de los Sprint 1 a 4 (Sprint 4: frontend hecho con datos simulados, backend en curso; casos manuales Pendientes). Se actualiza con los contadores de las hojas.</t>
         </is>
       </c>
     </row>
@@ -634,23 +634,23 @@
         </is>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$431,B8)</f>
+        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$449,B8)</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B8,'Parte B - Automatizados'!$J$2:$J$431,"OK")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B8,'Parte B - Automatizados'!$J$2:$J$431,"Falla")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"Falla")</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B8,'Parte B - Automatizados'!$J$2:$J$431,"Bloqueado")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B8,'Parte B - Automatizados'!$J$2:$J$431,"Pendiente")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"Pendiente")</f>
         <v/>
       </c>
     </row>
@@ -666,161 +666,193 @@
         </is>
       </c>
       <c r="C9" s="3">
-        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$431,B9)</f>
+        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$449,B9)</f>
         <v/>
       </c>
       <c r="D9" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"OK")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B9,'Parte B - Automatizados'!$J$2:$J$449,"OK")</f>
         <v/>
       </c>
       <c r="E9" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"Falla")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B9,'Parte B - Automatizados'!$J$2:$J$449,"Falla")</f>
         <v/>
       </c>
       <c r="F9" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"Bloqueado")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B9,'Parte B - Automatizados'!$J$2:$J$449,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G9" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$431,B9,'Parte B - Automatizados'!$J$2:$J$431,"Pendiente")</f>
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B9,'Parte B - Automatizados'!$J$2:$J$449,"Pendiente")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Automatizados (TA)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C10" s="3">
+        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$449,B10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B10,'Parte B - Automatizados'!$J$2:$J$449,"OK")</f>
+        <v/>
+      </c>
+      <c r="E10" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B10,'Parte B - Automatizados'!$J$2:$J$449,"Falla")</f>
+        <v/>
+      </c>
+      <c r="F10" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B10,'Parte B - Automatizados'!$J$2:$J$449,"Bloqueado")</f>
+        <v/>
+      </c>
+      <c r="G10" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B10,'Parte B - Automatizados'!$J$2:$J$449,"Pendiente")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
-      <c r="C10" s="4">
-        <f>SUM(C5:C9)</f>
+      <c r="B11" s="4" t="inlineStr"/>
+      <c r="C11" s="4">
+        <f>SUM(C5:C10)</f>
         <v/>
       </c>
-      <c r="D10" s="4">
-        <f>SUM(D5:D9)</f>
+      <c r="D11" s="4">
+        <f>SUM(D5:D10)</f>
         <v/>
       </c>
-      <c r="E10" s="4">
-        <f>SUM(E5:E9)</f>
+      <c r="E11" s="4">
+        <f>SUM(E5:E10)</f>
         <v/>
       </c>
-      <c r="F10" s="4">
-        <f>SUM(F5:F9)</f>
+      <c r="F11" s="4">
+        <f>SUM(F5:F10)</f>
         <v/>
       </c>
-      <c r="G10" s="4">
-        <f>SUM(G5:G9)</f>
+      <c r="G11" s="4">
+        <f>SUM(G5:G10)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Última ejecución (2026-10-12, rama dev)</t>
-        </is>
-      </c>
-    </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Backend: 246 pruebas unitarias y 240 de integración, todas OK.</t>
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Última ejecución (2026-10-14, rama dev con el trabajo de Sprint 4 integrado)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Frontend: 20 archivos / 51 pruebas y build de producción, OK.</t>
+          <t>Backend: 259 pruebas unitarias y 248 de integración, todas OK (incluye el endpoint de esquema de medicación, SCRUM-232).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UI en navegador real (Playwright): 33 de 33 verificaciones OK el 2026-10-09; no se volvió a correr el 2026-10-12 (necesita el stack completo).</t>
+          <t>Frontend: 29 archivos / 120 pruebas y build de producción, OK (incluye asistencia y medicación de Sprint 4, que usan datos simulados).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Prueba de humo por rol (Referente, Directora, Escucha, Coordinador): 11 de 15 pantallas OK; las 4 restantes son /inicio (ver Defectos y pendientes).</t>
+          <t>UI en navegador real (Playwright): 33 de 33 verificaciones OK el 2026-10-09; no se volvió a correr el 2026-10-12 (necesita el stack completo).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QA manual Sprint 1-2 (TC-01 a TC-40): 40 de 40 OK el 2026-10-06.</t>
+          <t>Prueba de humo por rol (Referente, Directora, Escucha, Coordinador): 11 de 15 pantallas OK; las 4 restantes son /inicio (ver Defectos y pendientes).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sprint 4: casos derivados de los criterios de aceptación de Jira, todos Pendientes hasta que haya desarrollo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+          <t>QA manual Sprint 1-2 (TC-01 a TC-40): 40 de 40 OK el 2026-10-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sprint 4: 48 casos manuales derivados de los criterios de Jira, todos Pendientes. Solo el esquema de medicación (SCRUM-232) tiene backend y tests; asistencia, agenda, stock e historial todavía no.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Épicas / historias cubiertas</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Sprint 1-2: EP-01 Fichas de personas · EP-02 Observaciones e historia de vida · EP-03 Cuentas, roles y notificaciones · EP-10 Asistencia · EP-12 Casa de Convivencia</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sprint 4: EP-10 Asistencia (SCRUM-54, 55, 56, 57) · Medicación (SCRUM-59, 60, 61, 71, 75)</t>
+          <t>Sprint 1-2: EP-01 Fichas de personas · EP-02 Observaciones e historia de vida · EP-03 Cuentas, roles y notificaciones · EP-10 Asistencia · EP-12 Casa de Convivencia</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Sprint 4: EP-10 Asistencia (SCRUM-54, 55, 56, 57) · Medicación (SCRUM-59, 60, 61, 71, 75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Sprint 3: EP-04 Calendario general y personal (SCRUM-15, 16, 17) · EP-05 Colaboradores (SCRUM-18, 19) y visitas de la Casa de Convivencia (SCRUM-74)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Hojas</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Parte A - Manuales: un caso por fila con sus pasos; el estado se completa desde la lista desplegable.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pasos TC: los TC del Sprint 1-2 con una fila por paso (#, Paso, Dato, Esperamos).</t>
+          <t>Parte A - Manuales: un caso por fila con sus pasos; el estado se completa desde la lista desplegable.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Parte B - Automatizados: un test xUnit por fila. Sprint 3 deriva su descripción del nombre del test.</t>
+          <t>Pasos TC: los TC del Sprint 1-2 con una fila por paso (#, Paso, Dato, Esperamos).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
+        <is>
+          <t>Parte B - Automatizados: un test xUnit por fila. Sprint 3 deriva su descripción del nombre del test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Defectos y pendientes: hallazgos de la ejecución y decisiones abiertas.</t>
         </is>
@@ -3384,7 +3416,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -3447,7 +3479,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -3510,7 +3542,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -3573,7 +3605,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -3636,7 +3668,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -3699,7 +3731,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3762,7 +3794,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -3825,7 +3857,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3888,7 +3920,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -3951,7 +3983,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -4014,7 +4046,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -4077,7 +4109,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -4140,7 +4172,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -4203,7 +4235,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -4266,7 +4298,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -4329,7 +4361,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -4392,7 +4424,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -4455,7 +4487,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -4518,7 +4550,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -4581,7 +4613,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -4644,7 +4676,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -4707,7 +4739,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -4770,7 +4802,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -4833,7 +4865,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4896,7 +4928,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -4959,7 +4991,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -5022,7 +5054,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -5085,7 +5117,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -5148,7 +5180,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -5211,7 +5243,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -5274,7 +5306,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -5337,7 +5369,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -5400,7 +5432,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -5463,7 +5495,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -5526,7 +5558,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -5589,7 +5621,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -5652,7 +5684,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -5715,7 +5747,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -5778,7 +5810,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -5841,7 +5873,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5904,7 +5936,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -5967,7 +5999,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -6030,7 +6062,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -6660,7 +6692,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -7105,7 +7137,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -7168,7 +7200,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -7231,7 +7263,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -7294,7 +7326,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -7357,7 +7389,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -7420,7 +7452,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -7483,7 +7515,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -7546,7 +7578,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -7609,7 +7641,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -7672,7 +7704,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -7735,7 +7767,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -7798,7 +7830,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -7861,7 +7893,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -7924,7 +7956,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -7987,7 +8019,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -8050,7 +8082,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -8113,7 +8145,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -8176,7 +8208,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -8239,7 +8271,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -8302,7 +8334,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -8365,7 +8397,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -8428,7 +8460,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -8491,7 +8523,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -8554,7 +8586,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -8617,7 +8649,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -8680,7 +8712,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -8743,7 +8775,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -8806,7 +8838,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -8869,7 +8901,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -8932,7 +8964,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -8995,7 +9027,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -9058,7 +9090,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -9121,7 +9153,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -9184,7 +9216,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -9247,7 +9279,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -9310,7 +9342,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -9373,7 +9405,7 @@
       </c>
       <c r="K137" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L137" s="7" t="inlineStr">
@@ -9436,7 +9468,7 @@
       </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L138" s="7" t="inlineStr">
@@ -9499,7 +9531,7 @@
       </c>
       <c r="K139" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L139" s="7" t="inlineStr">
@@ -9562,7 +9594,7 @@
       </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L140" s="7" t="inlineStr">
@@ -9625,7 +9657,7 @@
       </c>
       <c r="K141" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L141" s="7" t="inlineStr">
@@ -9688,7 +9720,7 @@
       </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L142" s="7" t="inlineStr">
@@ -9751,7 +9783,7 @@
       </c>
       <c r="K143" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L143" s="7" t="inlineStr">
@@ -9814,7 +9846,7 @@
       </c>
       <c r="K144" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L144" s="7" t="inlineStr">
@@ -9877,7 +9909,7 @@
       </c>
       <c r="K145" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L145" s="7" t="inlineStr">
@@ -9940,7 +9972,7 @@
       </c>
       <c r="K146" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L146" s="7" t="inlineStr">
@@ -10003,7 +10035,7 @@
       </c>
       <c r="K147" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L147" s="7" t="inlineStr">
@@ -11183,7 +11215,7 @@
       <c r="L168" s="7" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr">
         <is>
-          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+          <t>Backend (SCRUM-232) cubierto por tests automatizados; falta probar el formulario de punta a punta: hoy usa datos simulados.</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11270,7 @@
       <c r="L169" s="7" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr">
         <is>
-          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+          <t>Backend (SCRUM-232) cubierto por tests automatizados; falta probar el formulario de punta a punta: hoy usa datos simulados.</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11325,7 @@
       <c r="L170" s="7" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr">
         <is>
-          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+          <t>Backend (SCRUM-232) cubierto por tests automatizados; falta probar el formulario de punta a punta: hoy usa datos simulados.</t>
         </is>
       </c>
     </row>
@@ -11349,7 +11381,7 @@
       <c r="L171" s="7" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr">
         <is>
-          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+          <t>Backend (SCRUM-232) cubierto por tests automatizados; falta probar el formulario de punta a punta: hoy usa datos simulados.</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11436,7 @@
       <c r="L172" s="7" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr">
         <is>
-          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+          <t>Backend (SCRUM-232) cubierto por tests automatizados; falta probar el formulario de punta a punta: hoy usa datos simulados.</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11492,7 @@
       <c r="L173" s="7" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr">
         <is>
-          <t>Sin desarrollo todavía (Sprint 4 activo desde 2026-10-09).</t>
+          <t>Backend (SCRUM-232) cubierto por tests automatizados; falta probar el formulario de punta a punta: hoy usa datos simulados.</t>
         </is>
       </c>
     </row>
@@ -14975,7 +15007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L431"/>
+  <dimension ref="A1:L449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -15107,7 +15139,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -15169,7 +15201,7 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -15231,7 +15263,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -15294,7 +15326,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -15356,7 +15388,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
@@ -15418,7 +15450,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -15481,7 +15513,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -15543,7 +15575,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -15606,7 +15638,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -15668,7 +15700,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -15730,7 +15762,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -15792,7 +15824,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -15855,7 +15887,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -15917,7 +15949,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -15979,7 +16011,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -16042,7 +16074,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -16105,7 +16137,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -16168,7 +16200,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -16231,7 +16263,7 @@
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
@@ -16294,7 +16326,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -16356,7 +16388,7 @@
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
@@ -16418,7 +16450,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -16481,7 +16513,7 @@
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
@@ -16544,7 +16576,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -16607,7 +16639,7 @@
       </c>
       <c r="K26" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L26" s="7" t="inlineStr">
@@ -16669,7 +16701,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -16732,7 +16764,7 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
@@ -16795,7 +16827,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -16857,7 +16889,7 @@
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
@@ -16919,7 +16951,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -16982,7 +17014,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -17045,7 +17077,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -17108,7 +17140,7 @@
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
@@ -17171,7 +17203,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -17233,7 +17265,7 @@
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
@@ -17296,7 +17328,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -17358,7 +17390,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -17421,7 +17453,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -17484,7 +17516,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -17547,7 +17579,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -17609,7 +17641,7 @@
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
@@ -17672,7 +17704,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -17735,7 +17767,7 @@
       </c>
       <c r="K44" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L44" s="7" t="inlineStr">
@@ -17798,7 +17830,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -17860,7 +17892,7 @@
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
@@ -17923,7 +17955,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -17985,7 +18017,7 @@
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -18047,7 +18079,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -18109,7 +18141,7 @@
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
@@ -18171,7 +18203,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -18233,7 +18265,7 @@
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
@@ -18295,7 +18327,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -18357,7 +18389,7 @@
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
@@ -18419,7 +18451,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -18481,7 +18513,7 @@
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
@@ -18543,7 +18575,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -18605,7 +18637,7 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -18667,7 +18699,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -18729,7 +18761,7 @@
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
@@ -18792,7 +18824,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -18855,7 +18887,7 @@
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
@@ -18918,7 +18950,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -18981,7 +19013,7 @@
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
@@ -19044,7 +19076,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -19106,7 +19138,7 @@
       </c>
       <c r="K66" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L66" s="7" t="inlineStr">
@@ -19168,7 +19200,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -19230,7 +19262,7 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
@@ -19292,7 +19324,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -19354,7 +19386,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L70" s="7" t="inlineStr">
@@ -19416,7 +19448,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -19479,7 +19511,7 @@
       </c>
       <c r="K72" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L72" s="7" t="inlineStr">
@@ -19542,7 +19574,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -19605,7 +19637,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -19668,7 +19700,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -19730,7 +19762,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -19793,7 +19825,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -19855,7 +19887,7 @@
       </c>
       <c r="K78" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L78" s="7" t="inlineStr">
@@ -19917,7 +19949,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -19980,7 +20012,7 @@
       </c>
       <c r="K80" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L80" s="7" t="inlineStr">
@@ -20042,7 +20074,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -20105,7 +20137,7 @@
       </c>
       <c r="K82" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L82" s="7" t="inlineStr">
@@ -20167,7 +20199,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -20229,7 +20261,7 @@
       </c>
       <c r="K84" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L84" s="7" t="inlineStr">
@@ -20291,7 +20323,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -20353,7 +20385,7 @@
       </c>
       <c r="K86" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L86" s="7" t="inlineStr">
@@ -20415,7 +20447,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -20477,7 +20509,7 @@
       </c>
       <c r="K88" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L88" s="7" t="inlineStr">
@@ -20539,7 +20571,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -20601,7 +20633,7 @@
       </c>
       <c r="K90" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L90" s="7" t="inlineStr">
@@ -20664,7 +20696,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -20726,7 +20758,7 @@
       </c>
       <c r="K92" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L92" s="7" t="inlineStr">
@@ -20789,7 +20821,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -20852,7 +20884,7 @@
       </c>
       <c r="K94" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L94" s="7" t="inlineStr">
@@ -20915,7 +20947,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -20978,7 +21010,7 @@
       </c>
       <c r="K96" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L96" s="7" t="inlineStr">
@@ -21040,7 +21072,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -21102,7 +21134,7 @@
       </c>
       <c r="K98" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L98" s="7" t="inlineStr">
@@ -21164,7 +21196,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -21226,7 +21258,7 @@
       </c>
       <c r="K100" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L100" s="7" t="inlineStr">
@@ -21289,7 +21321,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -21352,7 +21384,7 @@
       </c>
       <c r="K102" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L102" s="7" t="inlineStr">
@@ -21415,7 +21447,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -21478,7 +21510,7 @@
       </c>
       <c r="K104" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L104" s="7" t="inlineStr">
@@ -21540,7 +21572,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -21602,7 +21634,7 @@
       </c>
       <c r="K106" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L106" s="7" t="inlineStr">
@@ -21664,7 +21696,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
@@ -21726,7 +21758,7 @@
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
@@ -21789,7 +21821,7 @@
       </c>
       <c r="K109" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L109" s="7" t="inlineStr">
@@ -21851,7 +21883,7 @@
       </c>
       <c r="K110" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L110" s="7" t="inlineStr">
@@ -21913,7 +21945,7 @@
       </c>
       <c r="K111" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L111" s="7" t="inlineStr">
@@ -21976,7 +22008,7 @@
       </c>
       <c r="K112" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L112" s="7" t="inlineStr">
@@ -22039,7 +22071,7 @@
       </c>
       <c r="K113" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L113" s="7" t="inlineStr">
@@ -22101,7 +22133,7 @@
       </c>
       <c r="K114" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L114" s="7" t="inlineStr">
@@ -22163,7 +22195,7 @@
       </c>
       <c r="K115" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L115" s="7" t="inlineStr">
@@ -22225,7 +22257,7 @@
       </c>
       <c r="K116" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L116" s="7" t="inlineStr">
@@ -22288,7 +22320,7 @@
       </c>
       <c r="K117" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L117" s="7" t="inlineStr">
@@ -22350,7 +22382,7 @@
       </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
@@ -22412,7 +22444,7 @@
       </c>
       <c r="K119" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L119" s="7" t="inlineStr">
@@ -22474,7 +22506,7 @@
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
@@ -22536,7 +22568,7 @@
       </c>
       <c r="K121" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L121" s="7" t="inlineStr">
@@ -22598,7 +22630,7 @@
       </c>
       <c r="K122" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L122" s="7" t="inlineStr">
@@ -22660,7 +22692,7 @@
       </c>
       <c r="K123" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L123" s="7" t="inlineStr">
@@ -22722,7 +22754,7 @@
       </c>
       <c r="K124" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L124" s="7" t="inlineStr">
@@ -22784,7 +22816,7 @@
       </c>
       <c r="K125" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L125" s="7" t="inlineStr">
@@ -22846,7 +22878,7 @@
       </c>
       <c r="K126" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L126" s="7" t="inlineStr">
@@ -22908,7 +22940,7 @@
       </c>
       <c r="K127" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L127" s="7" t="inlineStr">
@@ -22970,7 +23002,7 @@
       </c>
       <c r="K128" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L128" s="7" t="inlineStr">
@@ -23032,7 +23064,7 @@
       </c>
       <c r="K129" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L129" s="7" t="inlineStr">
@@ -23095,7 +23127,7 @@
       </c>
       <c r="K130" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L130" s="7" t="inlineStr">
@@ -23158,7 +23190,7 @@
       </c>
       <c r="K131" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L131" s="7" t="inlineStr">
@@ -23220,7 +23252,7 @@
       </c>
       <c r="K132" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L132" s="7" t="inlineStr">
@@ -23282,7 +23314,7 @@
       </c>
       <c r="K133" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L133" s="7" t="inlineStr">
@@ -23344,7 +23376,7 @@
       </c>
       <c r="K134" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L134" s="7" t="inlineStr">
@@ -23407,7 +23439,7 @@
       </c>
       <c r="K135" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L135" s="7" t="inlineStr">
@@ -23470,7 +23502,7 @@
       </c>
       <c r="K136" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L136" s="7" t="inlineStr">
@@ -23532,7 +23564,7 @@
       </c>
       <c r="K137" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L137" s="7" t="inlineStr">
@@ -23594,7 +23626,7 @@
       </c>
       <c r="K138" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L138" s="7" t="inlineStr">
@@ -23656,7 +23688,7 @@
       </c>
       <c r="K139" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L139" s="7" t="inlineStr">
@@ -23719,7 +23751,7 @@
       </c>
       <c r="K140" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L140" s="7" t="inlineStr">
@@ -23782,7 +23814,7 @@
       </c>
       <c r="K141" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L141" s="7" t="inlineStr">
@@ -23844,7 +23876,7 @@
       </c>
       <c r="K142" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L142" s="7" t="inlineStr">
@@ -23906,7 +23938,7 @@
       </c>
       <c r="K143" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L143" s="7" t="inlineStr">
@@ -23969,7 +24001,7 @@
       </c>
       <c r="K144" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L144" s="7" t="inlineStr">
@@ -24031,7 +24063,7 @@
       </c>
       <c r="K145" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L145" s="7" t="inlineStr">
@@ -24093,7 +24125,7 @@
       </c>
       <c r="K146" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L146" s="7" t="inlineStr">
@@ -24156,7 +24188,7 @@
       </c>
       <c r="K147" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L147" s="7" t="inlineStr">
@@ -24218,7 +24250,7 @@
       </c>
       <c r="K148" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L148" s="7" t="inlineStr">
@@ -24280,7 +24312,7 @@
       </c>
       <c r="K149" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L149" s="7" t="inlineStr">
@@ -24342,7 +24374,7 @@
       </c>
       <c r="K150" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L150" s="7" t="inlineStr">
@@ -24404,7 +24436,7 @@
       </c>
       <c r="K151" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L151" s="7" t="inlineStr">
@@ -24466,7 +24498,7 @@
       </c>
       <c r="K152" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L152" s="7" t="inlineStr">
@@ -24529,7 +24561,7 @@
       </c>
       <c r="K153" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L153" s="7" t="inlineStr">
@@ -24591,7 +24623,7 @@
       </c>
       <c r="K154" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L154" s="7" t="inlineStr">
@@ -24653,7 +24685,7 @@
       </c>
       <c r="K155" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L155" s="7" t="inlineStr">
@@ -24715,7 +24747,7 @@
       </c>
       <c r="K156" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L156" s="7" t="inlineStr">
@@ -24778,7 +24810,7 @@
       </c>
       <c r="K157" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L157" s="7" t="inlineStr">
@@ -24841,7 +24873,7 @@
       </c>
       <c r="K158" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L158" s="7" t="inlineStr">
@@ -24903,7 +24935,7 @@
       </c>
       <c r="K159" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L159" s="7" t="inlineStr">
@@ -24965,7 +24997,7 @@
       </c>
       <c r="K160" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L160" s="7" t="inlineStr">
@@ -25027,7 +25059,7 @@
       </c>
       <c r="K161" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L161" s="7" t="inlineStr">
@@ -25090,7 +25122,7 @@
       </c>
       <c r="K162" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L162" s="7" t="inlineStr">
@@ -25152,7 +25184,7 @@
       </c>
       <c r="K163" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L163" s="7" t="inlineStr">
@@ -25214,7 +25246,7 @@
       </c>
       <c r="K164" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L164" s="7" t="inlineStr">
@@ -25276,7 +25308,7 @@
       </c>
       <c r="K165" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L165" s="7" t="inlineStr">
@@ -25338,7 +25370,7 @@
       </c>
       <c r="K166" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L166" s="7" t="inlineStr">
@@ -25400,7 +25432,7 @@
       </c>
       <c r="K167" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L167" s="7" t="inlineStr">
@@ -25462,7 +25494,7 @@
       </c>
       <c r="K168" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L168" s="7" t="inlineStr">
@@ -25524,7 +25556,7 @@
       </c>
       <c r="K169" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L169" s="7" t="inlineStr">
@@ -25586,7 +25618,7 @@
       </c>
       <c r="K170" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L170" s="7" t="inlineStr">
@@ -25649,7 +25681,7 @@
       </c>
       <c r="K171" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L171" s="7" t="inlineStr">
@@ -25712,7 +25744,7 @@
       </c>
       <c r="K172" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L172" s="7" t="inlineStr">
@@ -25774,7 +25806,7 @@
       </c>
       <c r="K173" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L173" s="7" t="inlineStr">
@@ -25836,7 +25868,7 @@
       </c>
       <c r="K174" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L174" s="7" t="inlineStr">
@@ -25899,7 +25931,7 @@
       </c>
       <c r="K175" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L175" s="7" t="inlineStr">
@@ -25961,7 +25993,7 @@
       </c>
       <c r="K176" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L176" s="7" t="inlineStr">
@@ -26024,7 +26056,7 @@
       </c>
       <c r="K177" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L177" s="7" t="inlineStr">
@@ -26087,7 +26119,7 @@
       </c>
       <c r="K178" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L178" s="7" t="inlineStr">
@@ -26150,7 +26182,7 @@
       </c>
       <c r="K179" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L179" s="7" t="inlineStr">
@@ -26212,7 +26244,7 @@
       </c>
       <c r="K180" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L180" s="7" t="inlineStr">
@@ -26274,7 +26306,7 @@
       </c>
       <c r="K181" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L181" s="7" t="inlineStr">
@@ -26337,7 +26369,7 @@
       </c>
       <c r="K182" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L182" s="7" t="inlineStr">
@@ -26399,7 +26431,7 @@
       </c>
       <c r="K183" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L183" s="7" t="inlineStr">
@@ -26461,7 +26493,7 @@
       </c>
       <c r="K184" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L184" s="7" t="inlineStr">
@@ -26523,7 +26555,7 @@
       </c>
       <c r="K185" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L185" s="7" t="inlineStr">
@@ -26585,7 +26617,7 @@
       </c>
       <c r="K186" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L186" s="7" t="inlineStr">
@@ -26647,7 +26679,7 @@
       </c>
       <c r="K187" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L187" s="7" t="inlineStr">
@@ -26709,7 +26741,7 @@
       </c>
       <c r="K188" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L188" s="7" t="inlineStr">
@@ -26771,7 +26803,7 @@
       </c>
       <c r="K189" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L189" s="7" t="inlineStr">
@@ -26833,7 +26865,7 @@
       </c>
       <c r="K190" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L190" s="7" t="inlineStr">
@@ -26895,7 +26927,7 @@
       </c>
       <c r="K191" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L191" s="7" t="inlineStr">
@@ -26958,7 +26990,7 @@
       </c>
       <c r="K192" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L192" s="7" t="inlineStr">
@@ -27021,7 +27053,7 @@
       </c>
       <c r="K193" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L193" s="7" t="inlineStr">
@@ -27084,7 +27116,7 @@
       </c>
       <c r="K194" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L194" s="7" t="inlineStr">
@@ -27147,7 +27179,7 @@
       </c>
       <c r="K195" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L195" s="7" t="inlineStr">
@@ -27209,7 +27241,7 @@
       </c>
       <c r="K196" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L196" s="7" t="inlineStr">
@@ -27271,7 +27303,7 @@
       </c>
       <c r="K197" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L197" s="7" t="inlineStr">
@@ -27334,7 +27366,7 @@
       </c>
       <c r="K198" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L198" s="7" t="inlineStr">
@@ -27396,7 +27428,7 @@
       </c>
       <c r="K199" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L199" s="7" t="inlineStr">
@@ -27458,7 +27490,7 @@
       </c>
       <c r="K200" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L200" s="7" t="inlineStr">
@@ -27520,7 +27552,7 @@
       </c>
       <c r="K201" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L201" s="7" t="inlineStr">
@@ -27582,7 +27614,7 @@
       </c>
       <c r="K202" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L202" s="7" t="inlineStr">
@@ -27644,7 +27676,7 @@
       </c>
       <c r="K203" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L203" s="7" t="inlineStr">
@@ -27707,7 +27739,7 @@
       </c>
       <c r="K204" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L204" s="7" t="inlineStr">
@@ -27770,7 +27802,7 @@
       </c>
       <c r="K205" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L205" s="7" t="inlineStr">
@@ -27832,7 +27864,7 @@
       </c>
       <c r="K206" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L206" s="7" t="inlineStr">
@@ -27894,7 +27926,7 @@
       </c>
       <c r="K207" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L207" s="7" t="inlineStr">
@@ -27957,7 +27989,7 @@
       </c>
       <c r="K208" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L208" s="7" t="inlineStr">
@@ -28020,7 +28052,7 @@
       </c>
       <c r="K209" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L209" s="7" t="inlineStr">
@@ -28083,7 +28115,7 @@
       </c>
       <c r="K210" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L210" s="7" t="inlineStr">
@@ -28146,7 +28178,7 @@
       </c>
       <c r="K211" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L211" s="7" t="inlineStr">
@@ -28208,7 +28240,7 @@
       </c>
       <c r="K212" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L212" s="7" t="inlineStr">
@@ -28270,7 +28302,7 @@
       </c>
       <c r="K213" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L213" s="7" t="inlineStr">
@@ -28332,7 +28364,7 @@
       </c>
       <c r="K214" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L214" s="7" t="inlineStr">
@@ -28395,7 +28427,7 @@
       </c>
       <c r="K215" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L215" s="7" t="inlineStr">
@@ -28457,7 +28489,7 @@
       </c>
       <c r="K216" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L216" s="7" t="inlineStr">
@@ -28519,7 +28551,7 @@
       </c>
       <c r="K217" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L217" s="7" t="inlineStr">
@@ -28581,7 +28613,7 @@
       </c>
       <c r="K218" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L218" s="7" t="inlineStr">
@@ -28644,7 +28676,7 @@
       </c>
       <c r="K219" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L219" s="7" t="inlineStr">
@@ -28707,7 +28739,7 @@
       </c>
       <c r="K220" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L220" s="7" t="inlineStr">
@@ -28769,7 +28801,7 @@
       </c>
       <c r="K221" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L221" s="7" t="inlineStr">
@@ -28831,7 +28863,7 @@
       </c>
       <c r="K222" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L222" s="7" t="inlineStr">
@@ -28893,7 +28925,7 @@
       </c>
       <c r="K223" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L223" s="7" t="inlineStr">
@@ -28955,7 +28987,7 @@
       </c>
       <c r="K224" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L224" s="7" t="inlineStr">
@@ -29017,7 +29049,7 @@
       </c>
       <c r="K225" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L225" s="7" t="inlineStr">
@@ -29079,7 +29111,7 @@
       </c>
       <c r="K226" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L226" s="7" t="inlineStr">
@@ -29141,7 +29173,7 @@
       </c>
       <c r="K227" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L227" s="7" t="inlineStr">
@@ -29203,7 +29235,7 @@
       </c>
       <c r="K228" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L228" s="7" t="inlineStr">
@@ -29265,7 +29297,7 @@
       </c>
       <c r="K229" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L229" s="7" t="inlineStr">
@@ -29328,7 +29360,7 @@
       </c>
       <c r="K230" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L230" s="7" t="inlineStr">
@@ -29390,7 +29422,7 @@
       </c>
       <c r="K231" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L231" s="7" t="inlineStr">
@@ -29452,7 +29484,7 @@
       </c>
       <c r="K232" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L232" s="7" t="inlineStr">
@@ -29515,7 +29547,7 @@
       </c>
       <c r="K233" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L233" s="7" t="inlineStr">
@@ -29578,7 +29610,7 @@
       </c>
       <c r="K234" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L234" s="7" t="inlineStr">
@@ -29640,7 +29672,7 @@
       </c>
       <c r="K235" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L235" s="7" t="inlineStr">
@@ -29702,7 +29734,7 @@
       </c>
       <c r="K236" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L236" s="7" t="inlineStr">
@@ -29764,7 +29796,7 @@
       </c>
       <c r="K237" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L237" s="7" t="inlineStr">
@@ -29826,7 +29858,7 @@
       </c>
       <c r="K238" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L238" s="7" t="inlineStr">
@@ -29884,7 +29916,7 @@
       </c>
       <c r="K239" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L239" s="7" t="inlineStr">
@@ -29942,7 +29974,7 @@
       </c>
       <c r="K240" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L240" s="7" t="inlineStr">
@@ -30000,7 +30032,7 @@
       </c>
       <c r="K241" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L241" s="7" t="inlineStr">
@@ -30058,7 +30090,7 @@
       </c>
       <c r="K242" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L242" s="7" t="inlineStr">
@@ -30116,7 +30148,7 @@
       </c>
       <c r="K243" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L243" s="7" t="inlineStr">
@@ -30174,7 +30206,7 @@
       </c>
       <c r="K244" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L244" s="7" t="inlineStr">
@@ -30232,7 +30264,7 @@
       </c>
       <c r="K245" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L245" s="7" t="inlineStr">
@@ -30290,7 +30322,7 @@
       </c>
       <c r="K246" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L246" s="7" t="inlineStr">
@@ -30348,7 +30380,7 @@
       </c>
       <c r="K247" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L247" s="7" t="inlineStr">
@@ -30406,7 +30438,7 @@
       </c>
       <c r="K248" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L248" s="7" t="inlineStr">
@@ -30468,7 +30500,7 @@
       </c>
       <c r="K249" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L249" s="7" t="inlineStr">
@@ -30530,7 +30562,7 @@
       </c>
       <c r="K250" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L250" s="7" t="inlineStr">
@@ -30588,7 +30620,7 @@
       </c>
       <c r="K251" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L251" s="7" t="inlineStr">
@@ -30646,7 +30678,7 @@
       </c>
       <c r="K252" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L252" s="7" t="inlineStr">
@@ -30708,7 +30740,7 @@
       </c>
       <c r="K253" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L253" s="7" t="inlineStr">
@@ -30766,7 +30798,7 @@
       </c>
       <c r="K254" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L254" s="7" t="inlineStr">
@@ -30824,7 +30856,7 @@
       </c>
       <c r="K255" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L255" s="7" t="inlineStr">
@@ -30882,7 +30914,7 @@
       </c>
       <c r="K256" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L256" s="7" t="inlineStr">
@@ -30940,7 +30972,7 @@
       </c>
       <c r="K257" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L257" s="7" t="inlineStr">
@@ -30998,7 +31030,7 @@
       </c>
       <c r="K258" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L258" s="7" t="inlineStr">
@@ -31056,7 +31088,7 @@
       </c>
       <c r="K259" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L259" s="7" t="inlineStr">
@@ -31114,7 +31146,7 @@
       </c>
       <c r="K260" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L260" s="7" t="inlineStr">
@@ -31172,7 +31204,7 @@
       </c>
       <c r="K261" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L261" s="7" t="inlineStr">
@@ -31230,7 +31262,7 @@
       </c>
       <c r="K262" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L262" s="7" t="inlineStr">
@@ -31288,7 +31320,7 @@
       </c>
       <c r="K263" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L263" s="7" t="inlineStr">
@@ -31350,7 +31382,7 @@
       </c>
       <c r="K264" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L264" s="7" t="inlineStr">
@@ -31412,7 +31444,7 @@
       </c>
       <c r="K265" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L265" s="7" t="inlineStr">
@@ -31470,7 +31502,7 @@
       </c>
       <c r="K266" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L266" s="7" t="inlineStr">
@@ -31528,7 +31560,7 @@
       </c>
       <c r="K267" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L267" s="7" t="inlineStr">
@@ -31586,7 +31618,7 @@
       </c>
       <c r="K268" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L268" s="7" t="inlineStr">
@@ -31644,7 +31676,7 @@
       </c>
       <c r="K269" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L269" s="7" t="inlineStr">
@@ -31702,7 +31734,7 @@
       </c>
       <c r="K270" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L270" s="7" t="inlineStr">
@@ -31760,7 +31792,7 @@
       </c>
       <c r="K271" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L271" s="7" t="inlineStr">
@@ -31818,7 +31850,7 @@
       </c>
       <c r="K272" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L272" s="7" t="inlineStr">
@@ -31876,7 +31908,7 @@
       </c>
       <c r="K273" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L273" s="7" t="inlineStr">
@@ -31938,7 +31970,7 @@
       </c>
       <c r="K274" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L274" s="7" t="inlineStr">
@@ -32000,7 +32032,7 @@
       </c>
       <c r="K275" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L275" s="7" t="inlineStr">
@@ -32062,7 +32094,7 @@
       </c>
       <c r="K276" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L276" s="7" t="inlineStr">
@@ -32120,7 +32152,7 @@
       </c>
       <c r="K277" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L277" s="7" t="inlineStr">
@@ -32182,7 +32214,7 @@
       </c>
       <c r="K278" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L278" s="7" t="inlineStr">
@@ -32244,7 +32276,7 @@
       </c>
       <c r="K279" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L279" s="7" t="inlineStr">
@@ -32302,7 +32334,7 @@
       </c>
       <c r="K280" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L280" s="7" t="inlineStr">
@@ -32360,7 +32392,7 @@
       </c>
       <c r="K281" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L281" s="7" t="inlineStr">
@@ -32418,7 +32450,7 @@
       </c>
       <c r="K282" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L282" s="7" t="inlineStr">
@@ -32476,7 +32508,7 @@
       </c>
       <c r="K283" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L283" s="7" t="inlineStr">
@@ -32534,7 +32566,7 @@
       </c>
       <c r="K284" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L284" s="7" t="inlineStr">
@@ -32592,7 +32624,7 @@
       </c>
       <c r="K285" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L285" s="7" t="inlineStr">
@@ -32650,7 +32682,7 @@
       </c>
       <c r="K286" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L286" s="7" t="inlineStr">
@@ -32708,7 +32740,7 @@
       </c>
       <c r="K287" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L287" s="7" t="inlineStr">
@@ -32766,7 +32798,7 @@
       </c>
       <c r="K288" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L288" s="7" t="inlineStr">
@@ -32824,7 +32856,7 @@
       </c>
       <c r="K289" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L289" s="7" t="inlineStr">
@@ -32882,7 +32914,7 @@
       </c>
       <c r="K290" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L290" s="7" t="inlineStr">
@@ -32940,7 +32972,7 @@
       </c>
       <c r="K291" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L291" s="7" t="inlineStr">
@@ -32998,7 +33030,7 @@
       </c>
       <c r="K292" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L292" s="7" t="inlineStr">
@@ -33056,7 +33088,7 @@
       </c>
       <c r="K293" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L293" s="7" t="inlineStr">
@@ -33114,7 +33146,7 @@
       </c>
       <c r="K294" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L294" s="7" t="inlineStr">
@@ -33172,7 +33204,7 @@
       </c>
       <c r="K295" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L295" s="7" t="inlineStr">
@@ -33230,7 +33262,7 @@
       </c>
       <c r="K296" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L296" s="7" t="inlineStr">
@@ -33288,7 +33320,7 @@
       </c>
       <c r="K297" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L297" s="7" t="inlineStr">
@@ -33350,7 +33382,7 @@
       </c>
       <c r="K298" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L298" s="7" t="inlineStr">
@@ -33412,7 +33444,7 @@
       </c>
       <c r="K299" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L299" s="7" t="inlineStr">
@@ -33474,7 +33506,7 @@
       </c>
       <c r="K300" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L300" s="7" t="inlineStr">
@@ -33536,7 +33568,7 @@
       </c>
       <c r="K301" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L301" s="7" t="inlineStr">
@@ -33598,7 +33630,7 @@
       </c>
       <c r="K302" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L302" s="7" t="inlineStr">
@@ -33656,7 +33688,7 @@
       </c>
       <c r="K303" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L303" s="7" t="inlineStr">
@@ -33714,7 +33746,7 @@
       </c>
       <c r="K304" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L304" s="7" t="inlineStr">
@@ -33772,7 +33804,7 @@
       </c>
       <c r="K305" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L305" s="7" t="inlineStr">
@@ -33830,7 +33862,7 @@
       </c>
       <c r="K306" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L306" s="7" t="inlineStr">
@@ -33888,7 +33920,7 @@
       </c>
       <c r="K307" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L307" s="7" t="inlineStr">
@@ -33946,7 +33978,7 @@
       </c>
       <c r="K308" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L308" s="7" t="inlineStr">
@@ -34004,7 +34036,7 @@
       </c>
       <c r="K309" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L309" s="7" t="inlineStr">
@@ -34062,7 +34094,7 @@
       </c>
       <c r="K310" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L310" s="7" t="inlineStr">
@@ -34120,7 +34152,7 @@
       </c>
       <c r="K311" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L311" s="7" t="inlineStr">
@@ -34178,7 +34210,7 @@
       </c>
       <c r="K312" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L312" s="7" t="inlineStr">
@@ -34236,7 +34268,7 @@
       </c>
       <c r="K313" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L313" s="7" t="inlineStr">
@@ -34294,7 +34326,7 @@
       </c>
       <c r="K314" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L314" s="7" t="inlineStr">
@@ -34352,7 +34384,7 @@
       </c>
       <c r="K315" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L315" s="7" t="inlineStr">
@@ -34410,7 +34442,7 @@
       </c>
       <c r="K316" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L316" s="7" t="inlineStr">
@@ -34468,7 +34500,7 @@
       </c>
       <c r="K317" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L317" s="7" t="inlineStr">
@@ -34526,7 +34558,7 @@
       </c>
       <c r="K318" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L318" s="7" t="inlineStr">
@@ -34584,7 +34616,7 @@
       </c>
       <c r="K319" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L319" s="7" t="inlineStr">
@@ -34646,7 +34678,7 @@
       </c>
       <c r="K320" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L320" s="7" t="inlineStr">
@@ -34708,7 +34740,7 @@
       </c>
       <c r="K321" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L321" s="7" t="inlineStr">
@@ -34766,7 +34798,7 @@
       </c>
       <c r="K322" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L322" s="7" t="inlineStr">
@@ -34824,7 +34856,7 @@
       </c>
       <c r="K323" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L323" s="7" t="inlineStr">
@@ -34886,7 +34918,7 @@
       </c>
       <c r="K324" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L324" s="7" t="inlineStr">
@@ -34948,7 +34980,7 @@
       </c>
       <c r="K325" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L325" s="7" t="inlineStr">
@@ -35006,7 +35038,7 @@
       </c>
       <c r="K326" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L326" s="7" t="inlineStr">
@@ -35068,7 +35100,7 @@
       </c>
       <c r="K327" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L327" s="7" t="inlineStr">
@@ -35130,7 +35162,7 @@
       </c>
       <c r="K328" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L328" s="7" t="inlineStr">
@@ -35192,7 +35224,7 @@
       </c>
       <c r="K329" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L329" s="7" t="inlineStr">
@@ -35254,7 +35286,7 @@
       </c>
       <c r="K330" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L330" s="7" t="inlineStr">
@@ -35316,7 +35348,7 @@
       </c>
       <c r="K331" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L331" s="7" t="inlineStr">
@@ -35378,7 +35410,7 @@
       </c>
       <c r="K332" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L332" s="7" t="inlineStr">
@@ -35440,7 +35472,7 @@
       </c>
       <c r="K333" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L333" s="7" t="inlineStr">
@@ -35502,7 +35534,7 @@
       </c>
       <c r="K334" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L334" s="7" t="inlineStr">
@@ -35564,7 +35596,7 @@
       </c>
       <c r="K335" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L335" s="7" t="inlineStr">
@@ -35626,7 +35658,7 @@
       </c>
       <c r="K336" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L336" s="7" t="inlineStr">
@@ -35688,7 +35720,7 @@
       </c>
       <c r="K337" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L337" s="7" t="inlineStr">
@@ -35750,7 +35782,7 @@
       </c>
       <c r="K338" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L338" s="7" t="inlineStr">
@@ -35812,7 +35844,7 @@
       </c>
       <c r="K339" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L339" s="7" t="inlineStr">
@@ -35874,7 +35906,7 @@
       </c>
       <c r="K340" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L340" s="7" t="inlineStr">
@@ -35936,7 +35968,7 @@
       </c>
       <c r="K341" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L341" s="7" t="inlineStr">
@@ -35998,7 +36030,7 @@
       </c>
       <c r="K342" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L342" s="7" t="inlineStr">
@@ -36060,7 +36092,7 @@
       </c>
       <c r="K343" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L343" s="7" t="inlineStr">
@@ -36122,7 +36154,7 @@
       </c>
       <c r="K344" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L344" s="7" t="inlineStr">
@@ -36184,7 +36216,7 @@
       </c>
       <c r="K345" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L345" s="7" t="inlineStr">
@@ -36246,7 +36278,7 @@
       </c>
       <c r="K346" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L346" s="7" t="inlineStr">
@@ -36308,7 +36340,7 @@
       </c>
       <c r="K347" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L347" s="7" t="inlineStr">
@@ -36370,7 +36402,7 @@
       </c>
       <c r="K348" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L348" s="7" t="inlineStr">
@@ -36432,7 +36464,7 @@
       </c>
       <c r="K349" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L349" s="7" t="inlineStr">
@@ -36490,7 +36522,7 @@
       </c>
       <c r="K350" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L350" s="7" t="inlineStr">
@@ -36548,7 +36580,7 @@
       </c>
       <c r="K351" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L351" s="7" t="inlineStr">
@@ -36610,7 +36642,7 @@
       </c>
       <c r="K352" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L352" s="7" t="inlineStr">
@@ -36672,7 +36704,7 @@
       </c>
       <c r="K353" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L353" s="7" t="inlineStr">
@@ -36734,7 +36766,7 @@
       </c>
       <c r="K354" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L354" s="7" t="inlineStr">
@@ -36796,7 +36828,7 @@
       </c>
       <c r="K355" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L355" s="7" t="inlineStr">
@@ -36858,7 +36890,7 @@
       </c>
       <c r="K356" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L356" s="7" t="inlineStr">
@@ -36920,7 +36952,7 @@
       </c>
       <c r="K357" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L357" s="7" t="inlineStr">
@@ -36982,7 +37014,7 @@
       </c>
       <c r="K358" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L358" s="7" t="inlineStr">
@@ -37044,7 +37076,7 @@
       </c>
       <c r="K359" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L359" s="7" t="inlineStr">
@@ -37106,7 +37138,7 @@
       </c>
       <c r="K360" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L360" s="7" t="inlineStr">
@@ -37168,7 +37200,7 @@
       </c>
       <c r="K361" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L361" s="7" t="inlineStr">
@@ -37230,7 +37262,7 @@
       </c>
       <c r="K362" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L362" s="7" t="inlineStr">
@@ -37292,7 +37324,7 @@
       </c>
       <c r="K363" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L363" s="7" t="inlineStr">
@@ -37354,7 +37386,7 @@
       </c>
       <c r="K364" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L364" s="7" t="inlineStr">
@@ -37416,7 +37448,7 @@
       </c>
       <c r="K365" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L365" s="7" t="inlineStr">
@@ -37478,7 +37510,7 @@
       </c>
       <c r="K366" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L366" s="7" t="inlineStr">
@@ -37540,7 +37572,7 @@
       </c>
       <c r="K367" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L367" s="7" t="inlineStr">
@@ -37602,7 +37634,7 @@
       </c>
       <c r="K368" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L368" s="7" t="inlineStr">
@@ -37664,7 +37696,7 @@
       </c>
       <c r="K369" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L369" s="7" t="inlineStr">
@@ -37726,7 +37758,7 @@
       </c>
       <c r="K370" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L370" s="7" t="inlineStr">
@@ -37788,7 +37820,7 @@
       </c>
       <c r="K371" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L371" s="7" t="inlineStr">
@@ -37850,7 +37882,7 @@
       </c>
       <c r="K372" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L372" s="7" t="inlineStr">
@@ -37912,7 +37944,7 @@
       </c>
       <c r="K373" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L373" s="7" t="inlineStr">
@@ -37974,7 +38006,7 @@
       </c>
       <c r="K374" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L374" s="7" t="inlineStr">
@@ -38036,7 +38068,7 @@
       </c>
       <c r="K375" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L375" s="7" t="inlineStr">
@@ -38098,7 +38130,7 @@
       </c>
       <c r="K376" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L376" s="7" t="inlineStr">
@@ -38160,7 +38192,7 @@
       </c>
       <c r="K377" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L377" s="7" t="inlineStr">
@@ -38222,7 +38254,7 @@
       </c>
       <c r="K378" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L378" s="7" t="inlineStr">
@@ -38284,7 +38316,7 @@
       </c>
       <c r="K379" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L379" s="7" t="inlineStr">
@@ -38346,7 +38378,7 @@
       </c>
       <c r="K380" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L380" s="7" t="inlineStr">
@@ -38408,7 +38440,7 @@
       </c>
       <c r="K381" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L381" s="7" t="inlineStr">
@@ -38470,7 +38502,7 @@
       </c>
       <c r="K382" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L382" s="7" t="inlineStr">
@@ -38532,7 +38564,7 @@
       </c>
       <c r="K383" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L383" s="7" t="inlineStr">
@@ -38594,7 +38626,7 @@
       </c>
       <c r="K384" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L384" s="7" t="inlineStr">
@@ -38656,7 +38688,7 @@
       </c>
       <c r="K385" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L385" s="7" t="inlineStr">
@@ -38718,7 +38750,7 @@
       </c>
       <c r="K386" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L386" s="7" t="inlineStr">
@@ -38780,7 +38812,7 @@
       </c>
       <c r="K387" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L387" s="7" t="inlineStr">
@@ -38842,7 +38874,7 @@
       </c>
       <c r="K388" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L388" s="7" t="inlineStr">
@@ -38904,7 +38936,7 @@
       </c>
       <c r="K389" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L389" s="7" t="inlineStr">
@@ -38966,7 +38998,7 @@
       </c>
       <c r="K390" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L390" s="7" t="inlineStr">
@@ -39028,7 +39060,7 @@
       </c>
       <c r="K391" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L391" s="7" t="inlineStr">
@@ -39090,7 +39122,7 @@
       </c>
       <c r="K392" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L392" s="7" t="inlineStr">
@@ -39152,7 +39184,7 @@
       </c>
       <c r="K393" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L393" s="7" t="inlineStr">
@@ -39214,7 +39246,7 @@
       </c>
       <c r="K394" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L394" s="7" t="inlineStr">
@@ -39276,7 +39308,7 @@
       </c>
       <c r="K395" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L395" s="7" t="inlineStr">
@@ -39338,7 +39370,7 @@
       </c>
       <c r="K396" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L396" s="7" t="inlineStr">
@@ -39400,7 +39432,7 @@
       </c>
       <c r="K397" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L397" s="7" t="inlineStr">
@@ -39462,7 +39494,7 @@
       </c>
       <c r="K398" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L398" s="7" t="inlineStr">
@@ -39524,7 +39556,7 @@
       </c>
       <c r="K399" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L399" s="7" t="inlineStr">
@@ -39586,7 +39618,7 @@
       </c>
       <c r="K400" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L400" s="7" t="inlineStr">
@@ -39648,7 +39680,7 @@
       </c>
       <c r="K401" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L401" s="7" t="inlineStr">
@@ -39710,7 +39742,7 @@
       </c>
       <c r="K402" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L402" s="7" t="inlineStr">
@@ -39772,7 +39804,7 @@
       </c>
       <c r="K403" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L403" s="7" t="inlineStr">
@@ -39834,7 +39866,7 @@
       </c>
       <c r="K404" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L404" s="7" t="inlineStr">
@@ -39896,7 +39928,7 @@
       </c>
       <c r="K405" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L405" s="7" t="inlineStr">
@@ -39958,7 +39990,7 @@
       </c>
       <c r="K406" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L406" s="7" t="inlineStr">
@@ -40020,7 +40052,7 @@
       </c>
       <c r="K407" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L407" s="7" t="inlineStr">
@@ -40082,7 +40114,7 @@
       </c>
       <c r="K408" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L408" s="7" t="inlineStr">
@@ -40144,7 +40176,7 @@
       </c>
       <c r="K409" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L409" s="7" t="inlineStr">
@@ -40206,7 +40238,7 @@
       </c>
       <c r="K410" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L410" s="7" t="inlineStr">
@@ -40268,7 +40300,7 @@
       </c>
       <c r="K411" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L411" s="7" t="inlineStr">
@@ -40330,7 +40362,7 @@
       </c>
       <c r="K412" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L412" s="7" t="inlineStr">
@@ -40392,7 +40424,7 @@
       </c>
       <c r="K413" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L413" s="7" t="inlineStr">
@@ -40454,7 +40486,7 @@
       </c>
       <c r="K414" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L414" s="7" t="inlineStr">
@@ -40516,7 +40548,7 @@
       </c>
       <c r="K415" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L415" s="7" t="inlineStr">
@@ -40578,7 +40610,7 @@
       </c>
       <c r="K416" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L416" s="7" t="inlineStr">
@@ -40640,7 +40672,7 @@
       </c>
       <c r="K417" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L417" s="7" t="inlineStr">
@@ -40702,7 +40734,7 @@
       </c>
       <c r="K418" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L418" s="7" t="inlineStr">
@@ -40760,7 +40792,7 @@
       </c>
       <c r="K419" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L419" s="7" t="inlineStr">
@@ -40822,7 +40854,7 @@
       </c>
       <c r="K420" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L420" s="7" t="inlineStr">
@@ -40884,7 +40916,7 @@
       </c>
       <c r="K421" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L421" s="7" t="inlineStr">
@@ -40946,7 +40978,7 @@
       </c>
       <c r="K422" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L422" s="7" t="inlineStr">
@@ -41008,7 +41040,7 @@
       </c>
       <c r="K423" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L423" s="7" t="inlineStr">
@@ -41070,7 +41102,7 @@
       </c>
       <c r="K424" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L424" s="7" t="inlineStr">
@@ -41132,7 +41164,7 @@
       </c>
       <c r="K425" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L425" s="7" t="inlineStr">
@@ -41194,7 +41226,7 @@
       </c>
       <c r="K426" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L426" s="7" t="inlineStr">
@@ -41256,7 +41288,7 @@
       </c>
       <c r="K427" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L427" s="7" t="inlineStr">
@@ -41318,7 +41350,7 @@
       </c>
       <c r="K428" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L428" s="7" t="inlineStr">
@@ -41380,7 +41412,7 @@
       </c>
       <c r="K429" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L429" s="7" t="inlineStr">
@@ -41442,7 +41474,7 @@
       </c>
       <c r="K430" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L430" s="7" t="inlineStr">
@@ -41504,7 +41536,7 @@
       </c>
       <c r="K431" s="7" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="L431" s="7" t="inlineStr">
@@ -41513,10 +41545,1054 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="7" t="inlineStr">
+        <is>
+          <t>TA-431</t>
+        </is>
+      </c>
+      <c r="B432" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C432" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D432" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithValidDto · PersistsSchemeWithActorAndFullData</t>
+        </is>
+      </c>
+      <c r="E432" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F432" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G432" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H432" s="7" t="inlineStr"/>
+      <c r="I432" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithValidDto_PersistsSchemeWithActorAndFullData</t>
+        </is>
+      </c>
+      <c r="J432" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K432" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L432" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="7" t="inlineStr">
+        <is>
+          <t>TA-432</t>
+        </is>
+      </c>
+      <c r="B433" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C433" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D433" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithZeroStock · MarksPendingStock</t>
+        </is>
+      </c>
+      <c r="E433" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F433" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G433" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H433" s="7" t="inlineStr"/>
+      <c r="I433" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithZeroStock_MarksPendingStock</t>
+        </is>
+      </c>
+      <c r="J433" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K433" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L433" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="7" t="inlineStr">
+        <is>
+          <t>TA-433</t>
+        </is>
+      </c>
+      <c r="B434" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C434" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D434" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithUnknownPerson · ReturnsPersonNotFound</t>
+        </is>
+      </c>
+      <c r="E434" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F434" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G434" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H434" s="7" t="inlineStr"/>
+      <c r="I434" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithUnknownPerson_ReturnsPersonNotFound</t>
+        </is>
+      </c>
+      <c r="J434" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K434" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L434" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="7" t="inlineStr">
+        <is>
+          <t>TA-434</t>
+        </is>
+      </c>
+      <c r="B435" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C435" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D435" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithAmbulatoryPerson · ReturnsPersonNotResident</t>
+        </is>
+      </c>
+      <c r="E435" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F435" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G435" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H435" s="7" t="inlineStr"/>
+      <c r="I435" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithAmbulatoryPerson_ReturnsPersonNotResident</t>
+        </is>
+      </c>
+      <c r="J435" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K435" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L435" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="7" t="inlineStr">
+        <is>
+          <t>TA-435</t>
+        </is>
+      </c>
+      <c r="B436" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C436" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D436" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithoutValidEvaluation · ReturnsMissingPsychiatricEvaluation</t>
+        </is>
+      </c>
+      <c r="E436" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F436" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G436" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H436" s="7" t="inlineStr"/>
+      <c r="I436" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithoutValidEvaluation_ReturnsMissingPsychiatricEvaluation</t>
+        </is>
+      </c>
+      <c r="J436" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K436" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L436" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="7" t="inlineStr">
+        <is>
+          <t>TA-436</t>
+        </is>
+      </c>
+      <c r="B437" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C437" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D437" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithUnknownMedication · ReturnsMedicationNotFound</t>
+        </is>
+      </c>
+      <c r="E437" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F437" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G437" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H437" s="7" t="inlineStr"/>
+      <c r="I437" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithUnknownMedication_ReturnsMedicationNotFound</t>
+        </is>
+      </c>
+      <c r="J437" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K437" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L437" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="7" t="inlineStr">
+        <is>
+          <t>TA-437</t>
+        </is>
+      </c>
+      <c r="B438" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C438" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D438" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithDuplicateActiveScheme · ReturnsDuplicateScheme</t>
+        </is>
+      </c>
+      <c r="E438" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F438" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G438" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H438" s="7" t="inlineStr"/>
+      <c r="I438" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithDuplicateActiveScheme_ReturnsDuplicateScheme</t>
+        </is>
+      </c>
+      <c r="J438" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K438" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L438" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="7" t="inlineStr">
+        <is>
+          <t>TA-438</t>
+        </is>
+      </c>
+      <c r="B439" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C439" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D439" s="7" t="inlineStr">
+        <is>
+          <t>Validar: CreateAsync · WithHistoricalScheme · AllowsReload</t>
+        </is>
+      </c>
+      <c r="E439" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F439" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G439" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H439" s="7" t="inlineStr"/>
+      <c r="I439" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › CreateAsync_WithHistoricalScheme_AllowsReload</t>
+        </is>
+      </c>
+      <c r="J439" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K439" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L439" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="7" t="inlineStr">
+        <is>
+          <t>TA-439</t>
+        </is>
+      </c>
+      <c r="B440" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C440" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D440" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Validator · AcceptsValidDto</t>
+        </is>
+      </c>
+      <c r="E440" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F440" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G440" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H440" s="7" t="inlineStr"/>
+      <c r="I440" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › Validator_AcceptsValidDto</t>
+        </is>
+      </c>
+      <c r="J440" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K440" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L440" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="7" t="inlineStr">
+        <is>
+          <t>TA-440</t>
+        </is>
+      </c>
+      <c r="B441" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C441" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D441" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Validator · RejectsInvalidDto</t>
+        </is>
+      </c>
+      <c r="E441" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F441" s="7" t="inlineStr">
+        <is>
+          <t>Servicio con DbContext InMemory.</t>
+        </is>
+      </c>
+      <c r="G441" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H441" s="7" t="inlineStr"/>
+      <c r="I441" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.UnitTests › MedicationSchemeServiceTests › Validator_RejectsInvalidDto</t>
+        </is>
+      </c>
+      <c r="J441" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K441" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L441" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="7" t="inlineStr">
+        <is>
+          <t>TA-441</t>
+        </is>
+      </c>
+      <c r="B442" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C442" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D442" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · ResidenteConEvaluacionVigente · Devuelve201ConEsquemaCompleto</t>
+        </is>
+      </c>
+      <c r="E442" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F442" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G442" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H442" s="7" t="inlineStr"/>
+      <c r="I442" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_ResidenteConEvaluacionVigente_Devuelve201ConEsquemaCompleto</t>
+        </is>
+      </c>
+      <c r="J442" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K442" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L442" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="7" t="inlineStr">
+        <is>
+          <t>TA-442</t>
+        </is>
+      </c>
+      <c r="B443" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C443" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D443" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · SinStock · MarcaPendienteStock</t>
+        </is>
+      </c>
+      <c r="E443" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F443" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G443" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H443" s="7" t="inlineStr"/>
+      <c r="I443" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_SinStock_MarcaPendienteStock</t>
+        </is>
+      </c>
+      <c r="J443" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K443" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L443" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="7" t="inlineStr">
+        <is>
+          <t>TA-443</t>
+        </is>
+      </c>
+      <c r="B444" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C444" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D444" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · SinEvaluacionVigente · Devuelve400</t>
+        </is>
+      </c>
+      <c r="E444" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F444" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G444" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H444" s="7" t="inlineStr"/>
+      <c r="I444" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_SinEvaluacionVigente_Devuelve400</t>
+        </is>
+      </c>
+      <c r="J444" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K444" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L444" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="7" t="inlineStr">
+        <is>
+          <t>TA-444</t>
+        </is>
+      </c>
+      <c r="B445" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C445" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D445" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · MedicamentoFueraDeCatalogo · Devuelve404</t>
+        </is>
+      </c>
+      <c r="E445" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F445" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G445" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H445" s="7" t="inlineStr"/>
+      <c r="I445" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_MedicamentoFueraDeCatalogo_Devuelve404</t>
+        </is>
+      </c>
+      <c r="J445" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K445" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L445" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="7" t="inlineStr">
+        <is>
+          <t>TA-445</t>
+        </is>
+      </c>
+      <c r="B446" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C446" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D446" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · EsquemaDuplicadoVigente · Devuelve409</t>
+        </is>
+      </c>
+      <c r="E446" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F446" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G446" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H446" s="7" t="inlineStr"/>
+      <c r="I446" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_EsquemaDuplicadoVigente_Devuelve409</t>
+        </is>
+      </c>
+      <c r="J446" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K446" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L446" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="7" t="inlineStr">
+        <is>
+          <t>TA-446</t>
+        </is>
+      </c>
+      <c r="B447" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C447" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D447" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · ConRolEscucha · Devuelve403</t>
+        </is>
+      </c>
+      <c r="E447" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F447" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G447" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H447" s="7" t="inlineStr"/>
+      <c r="I447" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_ConRolEscucha_Devuelve403</t>
+        </is>
+      </c>
+      <c r="J447" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K447" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L447" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="7" t="inlineStr">
+        <is>
+          <t>TA-447</t>
+        </is>
+      </c>
+      <c r="B448" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C448" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D448" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · DirectoraConAmbulatorio · Devuelve404</t>
+        </is>
+      </c>
+      <c r="E448" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F448" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G448" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H448" s="7" t="inlineStr"/>
+      <c r="I448" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_DirectoraConAmbulatorio_Devuelve404</t>
+        </is>
+      </c>
+      <c r="J448" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K448" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L448" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="7" t="inlineStr">
+        <is>
+          <t>TA-448</t>
+        </is>
+      </c>
+      <c r="B449" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C449" s="7" t="inlineStr">
+        <is>
+          <t>Esquema de medicación</t>
+        </is>
+      </c>
+      <c r="D449" s="7" t="inlineStr">
+        <is>
+          <t>Validar: Create · HoraInvalida · Devuelve400</t>
+        </is>
+      </c>
+      <c r="E449" s="7" t="inlineStr">
+        <is>
+          <t>Sin TC manual asociado; descripción derivada del nombre del test.</t>
+        </is>
+      </c>
+      <c r="F449" s="7" t="inlineStr">
+        <is>
+          <t>API levantada con WebApplicationFactory.</t>
+        </is>
+      </c>
+      <c r="G449" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59</t>
+        </is>
+      </c>
+      <c r="H449" s="7" t="inlineStr"/>
+      <c r="I449" s="7" t="inlineStr">
+        <is>
+          <t>Vicaria.IntegrationTests › MedicationSchemesEndpointTests › Create_HoraInvalida_Devuelve400</t>
+        </is>
+      </c>
+      <c r="J449" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K449" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="L449" s="7" t="inlineStr">
+        <is>
+          <t>Suite automatizada</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L431"/>
+  <autoFilter ref="A1:L449"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J431" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J449" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,OK,Falla,Bloqueado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -41530,7 +42606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -41909,27 +42985,27 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Defecto</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Las ramas dev-backend y dev-frontend no tienen los cambios de dev.</t>
+          <t>Los specs de asistencia y medicación de dev-frontend-belen usaban sintaxis de Jasmine (done, toBeTrue, toBeFalse) y no compilaban con Vitest: 55 errores y ningún test corría.</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>SCRUM-218 a 250 (frontend)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Corregido en dev</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Sincronizar por PR antes de que sigan Emir y Belén.</t>
+          <t>Se convirtieron a promesas y toBe(true/false): 120 de 120 pruebas OK.</t>
         </is>
       </c>
     </row>
@@ -41939,17 +43015,17 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Brecha</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Jira: SCRUM-198 y SCRUM-215 (QA) siguen 'En curso'.</t>
+          <t>Las pantallas de asistencia y medicación del frontend usan servicios simulados (of(...).pipe(delay)) y no llaman a la API.</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Jira</t>
+          <t>SCRUM-218 a 250 (frontend)</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -41959,7 +43035,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Cerrar con el resultado de esta ejecución.</t>
+          <t>Integrarlas con el backend a medida que se complete; hasta entonces los criterios de negocio no están verificados.</t>
         </is>
       </c>
     </row>
@@ -41969,17 +43045,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Pregunta abierta</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>El primer criterio dice "Hogar de día, , Casona (diaria)": falta una actividad en el texto. A confirmar cuáles son.</t>
+          <t>dev-backend trae un global.json que exige SDK 9.0.x y falla en equipos con otros SDK. dev no lo tiene.</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>dev-backend</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -41989,7 +43065,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Consultar al equipo antes de implementar o probar.</t>
+          <t>Avisar a Santiago antes de sincronizar ramas. Esta PC ya tiene el SDK 9.0.319.</t>
         </is>
       </c>
     </row>
@@ -41999,17 +43075,17 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Pregunta abierta</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>No se define cuándo se "cierra" un día (¿automático a medianoche, manual por un Referente?). Necesario para el último criterio.</t>
+          <t>Las ramas dev-backend y dev-frontend no tienen los cambios de dev.</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>SCRUM-54</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -42019,7 +43095,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Consultar al equipo antes de implementar o probar.</t>
+          <t>Sincronizar por PR antes de que sigan Emir y Belén.</t>
         </is>
       </c>
     </row>
@@ -42029,17 +43105,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Pregunta abierta</t>
+          <t>Pendiente</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Pide actividades configurables por los Referentes pero no hay una historia para esa pantalla de configuración.</t>
+          <t>Jira: SCRUM-198 y SCRUM-215 (QA) siguen 'En curso'.</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>SCRUM-57</t>
+          <t>Jira</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -42049,7 +43125,7 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Consultar al equipo antes de implementar o probar.</t>
+          <t>Cerrar con el resultado de esta ejecución.</t>
         </is>
       </c>
     </row>
@@ -42064,12 +43140,12 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Los permisos del Coordinador de Casona no son consistentes entre historias (SCRUM-59 lo incluye, SCRUM-60, 61 y 71 no lo nombran).</t>
+          <t>El primer criterio dice "Hogar de día, , Casona (diaria)": falta una actividad en el texto. A confirmar cuáles son.</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>SCRUM-59 / 60 / 61 / 71</t>
+          <t>SCRUM-54</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -42094,27 +43170,117 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
+          <t>No se define cuándo se "cierra" un día (¿automático a medianoche, manual por un Referente?). Necesario para el último criterio.</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-54</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Pide actividades configurables por los Referentes pero no hay una historia para esa pantalla de configuración.</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-57</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Los permisos del Coordinador de Casona no son consistentes entre historias (SCRUM-59 lo incluye, SCRUM-60, 61 y 71 no lo nombran).</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-59 / 60 / 61 / 71</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Consultar al equipo antes de implementar o probar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
           <t>SCRUM-59 habla de "stock en farmacia" y SCRUM-71 de "stock del Centro Barrial": confirmar que son el mismo inventario.</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>SCRUM-59 / 71</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>Abierta</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>Consultar al equipo antes de implementar o probar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F19"/>
+  <autoFilter ref="A1:F22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/qa/Plan_de_pruebas_Sprint_1-4.xlsx
+++ b/docs/qa/Plan_de_pruebas_Sprint_1-4.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defectos y pendientes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parte A - Manuales'!$A$1:$M$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Parte A - Manuales'!$A$1:$M$212</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Pasos TC'!$A$1:$E$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Parte B - Automatizados'!$A$1:$L$449</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defectos y pendientes'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Defectos y pendientes'!$A$1:$F$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -538,23 +538,23 @@
         </is>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$195,B5)</f>
+        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$212,B5)</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"OK")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B5,'Parte A - Manuales'!$J$2:$J$212,"OK")</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"Falla")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B5,'Parte A - Manuales'!$J$2:$J$212,"Falla")</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"Bloqueado")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B5,'Parte A - Manuales'!$J$2:$J$212,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B5,'Parte A - Manuales'!$J$2:$J$195,"Pendiente")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B5,'Parte A - Manuales'!$J$2:$J$212,"Pendiente")</f>
         <v/>
       </c>
     </row>
@@ -570,23 +570,23 @@
         </is>
       </c>
       <c r="C6" s="3">
-        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$195,B6)</f>
+        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$212,B6)</f>
         <v/>
       </c>
       <c r="D6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"OK")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B6,'Parte A - Manuales'!$J$2:$J$212,"OK")</f>
         <v/>
       </c>
       <c r="E6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"Falla")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B6,'Parte A - Manuales'!$J$2:$J$212,"Falla")</f>
         <v/>
       </c>
       <c r="F6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"Bloqueado")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B6,'Parte A - Manuales'!$J$2:$J$212,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G6" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B6,'Parte A - Manuales'!$J$2:$J$195,"Pendiente")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B6,'Parte A - Manuales'!$J$2:$J$212,"Pendiente")</f>
         <v/>
       </c>
     </row>
@@ -602,55 +602,55 @@
         </is>
       </c>
       <c r="C7" s="3">
-        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$195,B7)</f>
+        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$212,B7)</f>
         <v/>
       </c>
       <c r="D7" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"OK")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B7,'Parte A - Manuales'!$J$2:$J$212,"OK")</f>
         <v/>
       </c>
       <c r="E7" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"Falla")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B7,'Parte A - Manuales'!$J$2:$J$212,"Falla")</f>
         <v/>
       </c>
       <c r="F7" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"Bloqueado")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B7,'Parte A - Manuales'!$J$2:$J$212,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G7" s="3">
-        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$195,B7,'Parte A - Manuales'!$J$2:$J$195,"Pendiente")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B7,'Parte A - Manuales'!$J$2:$J$212,"Pendiente")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Automatizados (TA)</t>
+          <t>Manuales (TC)</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Sprint 1-2</t>
+          <t>Transversal</t>
         </is>
       </c>
       <c r="C8" s="3">
-        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$449,B8)</f>
+        <f>COUNTIF('Parte A - Manuales'!$B$2:$B$212,B8)</f>
         <v/>
       </c>
       <c r="D8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"OK")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B8,'Parte A - Manuales'!$J$2:$J$212,"OK")</f>
         <v/>
       </c>
       <c r="E8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"Falla")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B8,'Parte A - Manuales'!$J$2:$J$212,"Falla")</f>
         <v/>
       </c>
       <c r="F8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"Bloqueado")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B8,'Parte A - Manuales'!$J$2:$J$212,"Bloqueado")</f>
         <v/>
       </c>
       <c r="G8" s="3">
-        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B8,'Parte B - Automatizados'!$J$2:$J$449,"Pendiente")</f>
+        <f>COUNTIFS('Parte A - Manuales'!$B$2:$B$212,B8,'Parte A - Manuales'!$J$2:$J$212,"Pendiente")</f>
         <v/>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sprint 3</t>
+          <t>Sprint 1-2</t>
         </is>
       </c>
       <c r="C9" s="3">
@@ -694,7 +694,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sprint 4</t>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C10" s="3">
@@ -719,140 +719,179 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Automatizados (TA)</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C11" s="3">
+        <f>COUNTIF('Parte B - Automatizados'!$B$2:$B$449,B11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B11,'Parte B - Automatizados'!$J$2:$J$449,"OK")</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B11,'Parte B - Automatizados'!$J$2:$J$449,"Falla")</f>
+        <v/>
+      </c>
+      <c r="F11" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B11,'Parte B - Automatizados'!$J$2:$J$449,"Bloqueado")</f>
+        <v/>
+      </c>
+      <c r="G11" s="3">
+        <f>COUNTIFS('Parte B - Automatizados'!$B$2:$B$449,B11,'Parte B - Automatizados'!$J$2:$J$449,"Pendiente")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4">
-        <f>SUM(C5:C10)</f>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4">
+        <f>SUM(C5:C11)</f>
         <v/>
       </c>
-      <c r="D11" s="4">
-        <f>SUM(D5:D10)</f>
+      <c r="D12" s="4">
+        <f>SUM(D5:D11)</f>
         <v/>
       </c>
-      <c r="E11" s="4">
-        <f>SUM(E5:E10)</f>
+      <c r="E12" s="4">
+        <f>SUM(E5:E11)</f>
         <v/>
       </c>
-      <c r="F11" s="4">
-        <f>SUM(F5:F10)</f>
+      <c r="F12" s="4">
+        <f>SUM(F5:F11)</f>
         <v/>
       </c>
-      <c r="G11" s="4">
-        <f>SUM(G5:G10)</f>
+      <c r="G12" s="4">
+        <f>SUM(G5:G11)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Última ejecución (2026-10-14, rama dev con el trabajo de Sprint 4 integrado)</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Backend: 259 pruebas unitarias y 248 de integración, todas OK (incluye el endpoint de esquema de medicación, SCRUM-232).</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Última ejecución (2026-10-16, rama dev + correcciones de QA)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Frontend: 29 archivos / 120 pruebas y build de producción, OK (incluye asistencia y medicación de Sprint 4, que usan datos simulados).</t>
+          <t>Backend: ver cifras de la corrida en el informe (unitarias e integración, todas OK; el 16/10 se agregó un test unitario por el aviso de bloqueo en el 5º intento).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UI en navegador real (Playwright): 33 de 33 verificaciones OK el 2026-10-09; no se volvió a correr el 2026-10-12 (necesita el stack completo).</t>
+          <t>Frontend: 29 archivos / 122 pruebas y build de producción, OK.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Prueba de humo por rol (Referente, Directora, Escucha, Coordinador): 11 de 15 pantallas OK; las 4 restantes son /inicio (ver Defectos y pendientes).</t>
+          <t>UI en navegador real (Playwright): sprint1-2-ui-flows.mjs, 35 de 35 verificaciones OK tras corregir 6 defectos hallados en la primera pasada (#22 a #27).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QA manual Sprint 1-2 (TC-01 a TC-40): 40 de 40 OK el 2026-10-06.</t>
+          <t>Matriz rol x pantalla (Referente, Directora, Escucha, Coordinador): permisos correctos en todas las rutas; solo 'Informes' apunta a /inicio (#5).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sprint 4: 48 casos manuales derivados de los criterios de Jira, todos Pendientes. Solo el esquema de medicación (SCRUM-232) tiene backend y tests; asistencia, agenda, stock e historial todavía no.</t>
+          <t>Seguridad y carga (security/api-security-and-load.mjs): 13 verificaciones de seguridad y 4 de carga OK, sin errores bajo 50 usuarios concurrentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>QA manual Sprint 1-2 (TC-01 a TC-40): 40 de 40 OK; 23 de ellos se re-ejecutaron en navegador real el 2026-10-16.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sprint 4: 48 casos manuales derivados de los criterios de Jira, todos Pendientes (backend sin desarrollar salvo SCRUM-232).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Épicas / historias cubiertas</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Sprint 1-2: EP-01 Fichas de personas · EP-02 Observaciones e historia de vida · EP-03 Cuentas, roles y notificaciones · EP-10 Asistencia · EP-12 Casa de Convivencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Sprint 4: EP-10 Asistencia (SCRUM-54, 55, 56, 57) · Medicación (SCRUM-59, 60, 61, 71, 75)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Sprint 1-2: EP-01 Fichas de personas · EP-02 Observaciones e historia de vida · EP-03 Cuentas, roles y notificaciones · EP-10 Asistencia · EP-12 Casa de Convivencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sprint 4: EP-10 Asistencia (SCRUM-54, 55, 56, 57) · Medicación (SCRUM-59, 60, 61, 71, 75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Sprint 3: EP-04 Calendario general y personal (SCRUM-15, 16, 17) · EP-05 Colaboradores (SCRUM-18, 19) y visitas de la Casa de Convivencia (SCRUM-74)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Hojas</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Parte A - Manuales: un caso por fila con sus pasos; el estado se completa desde la lista desplegable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pasos TC: los TC del Sprint 1-2 con una fila por paso (#, Paso, Dato, Esperamos).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Parte B - Automatizados: un test xUnit por fila. Sprint 3 deriva su descripción del nombre del test.</t>
+          <t>Parte A - Manuales: un caso por fila con sus pasos; el estado se completa desde la lista desplegable.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
+        <is>
+          <t>Pasos TC: los TC del Sprint 1-2 con una fila por paso (#, Paso, Dato, Esperamos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Parte B - Automatizados: un test xUnit por fila. Sprint 3 deriva su descripción del nombre del test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Defectos y pendientes: hallazgos de la ejecución y decisiones abiertas.</t>
         </is>
@@ -869,7 +908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M195"/>
+  <dimension ref="A1:M212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -997,7 +1036,11 @@
 3. Intentar iniciar sesión con las credenciales recién creadas.  →  El sistema informa que la cuenta está "Pendiente de aprobación" y no permite el acceso.</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr"/>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1005,7 +1048,7 @@
       </c>
       <c r="K2" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L2" s="7" t="inlineStr">
@@ -1013,7 +1056,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Registro desde la UI: la cuenta queda en /auth/pending-approval y un login con esa cuenta vuelve a la pantalla de pendiente.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -1058,7 +1105,11 @@
 3. Seleccionar el rol Escucha y confirmar.  →  La cuenta pasa a estado "Activa" con el rol Escucha asignado.</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1066,7 +1117,7 @@
       </c>
       <c r="K3" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L3" s="7" t="inlineStr">
@@ -1074,7 +1125,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Un Referente aprueba la cuenta desde Usuarios &gt; Pendientes eligiendo el rol; desaparece de Pendientes y la cuenta ingresa al dashboard.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -1117,7 +1172,11 @@
           <t>1. Ingresar el correo electrónico y la contraseña, y hacer clic en Entrar.  →  El sistema valida las credenciales y redirige al panel principal según el rol del usuario.</t>
         </is>
       </c>
-      <c r="I4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1125,7 +1184,7 @@
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
@@ -1133,7 +1192,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Con clave incorrecta se muestra 'Correo o contraseña incorrectos.', no se ingresa y se limpia la contraseña.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -1178,7 +1241,11 @@
 3. Intentar iniciar sesión nuevamente con la contraseña correcta.  →  El sistema no permite el acceso mientras la cuenta permanezca bloqueada.</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1186,7 +1253,7 @@
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
@@ -1194,7 +1261,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>FALLÓ en la primera ejecución en navegador (DEF-22, DEF-23); corregido y re-ejecutado OK. Primera ejecución: el 5º intento respondía 401 sin avisar del bloqueo y, con la clave correcta, el login navegaba a /auth/blocked (ruta inexistente, pantalla en blanco). Tras la corrección: el 5º intento devuelve 403 y muestra 'Alcanzaste el máximo de intentos permitidos: tu cuenta quedó bloqueada por 30 minutos.'; con la clave correcta la cuenta sigue bloqueada.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1360,7 +1431,11 @@
 2. Intentar iniciar sesión con las credenciales de la cuenta desactivada.  →  El sistema deniega el acceso e informa que la cuenta se encuentra desactivada.</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1368,7 +1443,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
@@ -1376,7 +1451,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr">
+        <is>
+          <t>FALLÓ en la primera ejecución en navegador (DEF-24); corregido y re-ejecutado OK. Primera ejecución: la cuenta desactivada no ingresaba pero veía 'No pudimos iniciar sesión. Probá de nuevo en unos minutos.'. Tras la corrección muestra 'Tu cuenta está desactivada. Contactá a un Referente para reactivarla.'.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -1420,7 +1499,11 @@
 2. Abrir la ficha donde se registró la observación previa.  →  La observación se sigue mostrando en la línea de tiempo con su autor y fecha originales.</t>
         </is>
       </c>
-      <c r="I9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1428,7 +1511,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -1436,7 +1519,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Inactivar desde Usuarios mueve la cuenta a Inactivos; al reactivarla vuelve a ingresar al dashboard.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1480,7 +1567,11 @@
 2. Iniciar sesión como Referente y revisar el panel de notificaciones.  →  Se muestra una notificación indicando que hay una cuenta pendiente de aprobación.</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1488,7 +1579,7 @@
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -1496,7 +1587,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Al registrarse una cuenta, el Referente ve la notificación en la campana y el contador de no leídas aumenta.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -1601,7 +1696,11 @@
 3. Intentar guardar otra ficha dejando el nombre vacío.  →  El sistema rechaza el guardado e indica que el nombre es obligatorio.</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr"/>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1609,7 +1708,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
@@ -1617,7 +1716,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Alta mínima (nombre, apellido, DNI): la ficha se crea y aparece en el listado y el detalle. Una ficha vacía muestra los obligatorios y un DNI con letras muestra 'El DNI solo puede tener números, sin puntos ni espacios.'.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1661,7 +1764,11 @@
 2. Abrir una ficha.  →  La ficha se visualiza sin opciones de edición.</t>
         </is>
       </c>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1669,7 +1776,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1677,7 +1784,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>FALLÓ en la primera ejecución en navegador (DEF-26); corregido y re-ejecutado OK. Primera ejecución: Escucha veía 'Editar ficha' en el detalle y el ícono de editar en el listado. Tras la corrección no los ve, no ve 'Nueva ficha' y /edit lo redirige a acceso denegado.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1722,7 +1833,11 @@
 3. Buscar un texto sin coincidencias.  →  El sistema muestra una lista vacía, sin error.</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr"/>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1730,7 +1845,7 @@
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -1738,7 +1853,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Buscar 'jose&lt;n&gt; nunez' encuentra 'José&lt;n&gt; Núñez'; la búsqueda por DNI la encuentra y una búsqueda sin coincidencias no lista fichas.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -1782,7 +1901,11 @@
 2. Repetir con una fecha de ingreso futura.  →  El sistema rechaza el guardado con el mismo mensaje.</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1790,7 +1913,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1798,7 +1921,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>FALLÓ en la primera ejecución en navegador (DEF-25); corregido y re-ejecutado OK. Primera ejecución: con fecha futura la UI mostraba el mensaje genérico 'Ocurrió un error al guardar la ficha.'. Tras la corrección muestra el motivo de la API ('...no puede ser futura.') y no guarda.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -1843,7 +1970,11 @@
 3. Cambiar de página con un listado de más de una página.  →  La paginación refleja el total real de resultados.</t>
         </is>
       </c>
-      <c r="I16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1851,7 +1982,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
@@ -1859,7 +1990,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. El filtro por DNI del listado se aplica sin errores de API y muestra el filtro activo.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -1903,7 +2038,11 @@
 2. Elegir una categoría, escribir el texto y guardar.  →  Se muestra el modal de éxito y la observación aparece en la línea de tiempo con autor y fecha.</t>
         </is>
       </c>
-      <c r="I17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1911,7 +2050,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1919,7 +2058,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Se registra una observación con categoría (6 disponibles) y aparece en la línea de tiempo con su autor.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -1963,7 +2106,11 @@
 2. Filtrar por una categoría.  →  Solo se muestran las observaciones de esa categoría y el conteo coincide.</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -1971,7 +2118,7 @@
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
@@ -1979,7 +2126,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M18" s="7" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Filtrar por categoría deja solo las observaciones de esa categoría y el filtro por autor responde sin errores.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -2024,7 +2175,11 @@
 3. Exportar con un filtro sin resultados.  →  El CSV contiene solo el encabezado.</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr"/>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2032,7 +2187,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -2040,7 +2195,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. 'Exportar informe' descarga observaciones_&lt;id&gt;.csv.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -2144,7 +2303,11 @@
 2. Volver a guardar la misma etapa con otro texto.  →  Se ve el contenido nuevo y el anterior permanece en el historial.</t>
         </is>
       </c>
-      <c r="I21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2152,7 +2315,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -2160,7 +2323,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. La historia de vida muestra las 3 etapas y se agrega una entrada en la primera.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -2505,7 +2672,11 @@
 2. Intentar la misma acción por API.  →  El sistema responde 403 (CannotActOnSelf).</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2513,7 +2684,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -2521,7 +2692,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M27" s="7" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. En la fila de la propia cuenta, 'Reasignar Rol' e 'Inactivar' están deshabilitados.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -2804,7 +2979,11 @@
           <t>1. Ingresar a la pantalla de Login y hacer clic en Entrar sin completar nada.  →  El formulario solicita completar los campos y no se envía ninguna solicitud al servidor.</t>
         </is>
       </c>
-      <c r="I32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2812,7 +2991,7 @@
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
@@ -2820,7 +2999,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Login vacío: se muestran 'El correo electrónico es obligatorio.' y 'La contraseña es obligatoria.' y no se envía la petición.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
@@ -2864,7 +3047,11 @@
 2. Hacer clic en Registrarme.  →  El sistema rechaza el registro (409) e informa que el correo ya está registrado.</t>
         </is>
       </c>
-      <c r="I33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2872,7 +3059,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2880,7 +3067,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M33" s="7" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Registrar un correo existente muestra 'Ya existe un usuario registrado con ese email.' y permanece en el formulario.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -2985,7 +3176,11 @@
 2. Modificar un dato y guardar.  →  El sistema guarda los cambios y los muestra en el perfil de la ficha.</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -2993,7 +3188,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -3001,7 +3196,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M35" s="7" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. La edición carga el nombre guardado y los cambios se guardan y se ven en el detalle.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -3165,7 +3364,11 @@
 2. Elegir una categoría, dejar el texto vacío y guardar.  →  El formulario rechaza el guardado y no se crea ninguna observación.</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3173,7 +3376,7 @@
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
@@ -3181,7 +3384,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M38" s="7" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. Con el texto vacío el botón Guardar está deshabilitado y el modal sigue abierto.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -3225,7 +3432,11 @@
 2. Intentar guardar.  →  No se suma una entrada en blanco al historial de la etapa.</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3233,7 +3444,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -3241,7 +3452,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M39" s="7" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr">
+        <is>
+          <t>FALLÓ en la primera ejecución en navegador (DEF-27); corregido y re-ejecutado OK. Primera ejecución: con solo espacios el botón quedaba habilitado y la API respondía 400. Tras la corrección el botón queda deshabilitado.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -3285,7 +3500,11 @@
 2. Observar el contenido principal.  →  El contenido usa todo el ancho disponible de la pantalla.</t>
         </is>
       </c>
-      <c r="I40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3293,7 +3512,7 @@
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
@@ -3301,7 +3520,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. En 390 px de ancho no hay desborde horizontal en el inicio ni en el listado de fichas.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -3345,7 +3568,11 @@
 2. Elegir otra sección del menú.  →  El sistema navega a la sección elegida y el menú lateral se cierra automáticamente.</t>
         </is>
       </c>
-      <c r="I41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
           <t>OK</t>
@@ -3353,7 +3580,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -3361,7 +3588,11 @@
           <t>Mateo Pavoni</t>
         </is>
       </c>
-      <c r="M41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr">
+        <is>
+          <t>OK en navegador real. En pantalla chica el menú se abre con el botón y se oculta al elegir una opción.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -12716,10 +12947,1157 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>TC-195</t>
+        </is>
+      </c>
+      <c r="B196" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C196" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>Los endpoints protegidos exigen sesión</t>
+        </is>
+      </c>
+      <c r="E196" s="7" t="inlineStr">
+        <is>
+          <t>Sin token, la API no entrega datos.</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>1. GET de 7 rutas protegidas (fichas, listado, usuarios, notificaciones, colaboradores, calendarios) sin Authorization  →  Todas responden 401</t>
+        </is>
+      </c>
+      <c r="I196" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J196" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K196" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L196" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M196" s="7" t="inlineStr">
+        <is>
+          <t>Las 7 rutas respondieron 401.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
+        <is>
+          <t>TC-196</t>
+        </is>
+      </c>
+      <c r="B197" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C197" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D197" s="7" t="inlineStr">
+        <is>
+          <t>Autorización por rol en la API</t>
+        </is>
+      </c>
+      <c r="E197" s="7" t="inlineStr">
+        <is>
+          <t>Cada rol solo accede a lo que le corresponde.</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>1. Escucha intenta POST api/social-records  →  403
+2. Escucha, Coordinador y Directora piden api/auth/users/active  →  403</t>
+        </is>
+      </c>
+      <c r="I197" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J197" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K197" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L197" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M197" s="7" t="inlineStr">
+        <is>
+          <t>Crear ficha como Escucha: 403. Listar usuarios como Escucha, Coordinador y Directora: 403.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>TC-197</t>
+        </is>
+      </c>
+      <c r="B198" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C198" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>Un token manipulado se rechaza</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>Un JWT con el rol alterado, sin firma válida o malformado no da acceso.</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>1. Cambiar el rol del payload a Referente conservando la firma  →  401
+2. Token con alg=none  →  401
+3. Token malformado  →  401</t>
+        </is>
+      </c>
+      <c r="I198" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J198" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K198" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L198" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M198" s="7" t="inlineStr">
+        <is>
+          <t>Firma alterada, alg=none y token malformado: 401 en los tres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
+        <is>
+          <t>TC-198</t>
+        </is>
+      </c>
+      <c r="B199" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C199" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D199" s="7" t="inlineStr">
+        <is>
+          <t>Inyección SQL en la búsqueda</t>
+        </is>
+      </c>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
+          <t>La búsqueda está parametrizada.</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>1. Buscar "' OR 1=1 --" y "'; DROP TABLE Persons; --"  →  Sin error 500 y sin devolver todo el listado</t>
+        </is>
+      </c>
+      <c r="I199" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K199" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M199" s="7" t="inlineStr">
+        <is>
+          <t>Sin errores 500; la búsqueda devolvió 4 de 15 fichas por coincidencia de texto (no un OR 1=1) y las tablas siguen intactas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t>TC-199</t>
+        </is>
+      </c>
+      <c r="B200" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C200" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>El login no revela si el correo existe</t>
+        </is>
+      </c>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
+          <t>Mismo mensaje para correo inexistente y clave incorrecta.</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>1. Login con correo inexistente  →  401 'Credenciales inválidas.'
+2. Login con correo existente y clave incorrecta  →  Misma respuesta</t>
+        </is>
+      </c>
+      <c r="I200" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J200" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K200" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M200" s="7" t="inlineStr">
+        <is>
+          <t>Ambas respuestas fueron 401 con el mismo cuerpo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
+        <is>
+          <t>TC-200</t>
+        </is>
+      </c>
+      <c r="B201" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C201" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D201" s="7" t="inlineStr">
+        <is>
+          <t>Política de contraseñas</t>
+        </is>
+      </c>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>El registro rechaza contraseñas débiles.</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>1. Registrar con la contraseña '123'  →  400</t>
+        </is>
+      </c>
+      <c r="I201" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J201" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K201" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M201" s="7" t="inlineStr">
+        <is>
+          <t>Respondió 400.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>TC-201</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>Asignación masiva en el registro</t>
+        </is>
+      </c>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>Enviar role, roleId y status en el registro no otorga privilegios.</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>1. Registrar enviando role=Referente, roleId y status=Active  →  La cuenta queda Pendiente
+2. Intentar loguear  →  403 Pending</t>
+        </is>
+      </c>
+      <c r="I202" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J202" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K202" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L202" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M202" s="7" t="inlineStr">
+        <is>
+          <t>Registro 201 y login 403 con estado Pending: los campos extra se ignoran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
+        <is>
+          <t>TC-202</t>
+        </is>
+      </c>
+      <c r="B203" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C203" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="inlineStr">
+        <is>
+          <t>XSS: la API no cae ante HTML en los datos</t>
+        </is>
+      </c>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
+          <t>Un nombre con HTML no produce errores del servidor.</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>1. Crear una ficha con nombre '&lt;img src=x onerror=...&gt;'  →  Rechazo 4xx o guardado sin error 500</t>
+        </is>
+      </c>
+      <c r="I203" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J203" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K203" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M203" s="7" t="inlineStr">
+        <is>
+          <t>La API respondió 400 (nombre inválido).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="7" t="inlineStr">
+        <is>
+          <t>TC-203</t>
+        </is>
+      </c>
+      <c r="B204" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C204" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>XSS almacenado en una observación (UI)</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>El texto con HTML/script se muestra como texto y no ejecuta código.</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="inlineStr">
+        <is>
+          <t>1. Registrar una observación con &lt;img onerror&gt; y &lt;script&gt;  →  Se muestra el texto literal
+2. Verificar que no se ejecutó código en la página  →  window.__xss no está definido</t>
+        </is>
+      </c>
+      <c r="I204" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/e2e/sprint1-2-ui-flows.mjs</t>
+        </is>
+      </c>
+      <c r="J204" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K204" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L204" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M204" s="7" t="inlineStr">
+        <is>
+          <t>La observación se muestra como texto y no se ejecutó ningún script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>TC-204</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>Cabeceras de seguridad del frontend</t>
+        </is>
+      </c>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
+          <t>El servidor web envía cabeceras defensivas.</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>1. Pedir /auth y revisar cabeceras  →  X-Content-Type-Options, X-Frame-Options, Content-Security-Policy y Referrer-Policy presentes</t>
+        </is>
+      </c>
+      <c r="I205" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J205" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K205" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L205" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M205" s="7" t="inlineStr">
+        <is>
+          <t>Las cuatro cabeceras están presentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="7" t="inlineStr">
+        <is>
+          <t>TC-205</t>
+        </is>
+      </c>
+      <c r="B206" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C206" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>La API no expone la versión del servidor</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
+          <t>Sin X-Powered-By ni versión en Server.</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H206" s="7" t="inlineStr">
+        <is>
+          <t>1. Pedir una ruta de la API y revisar cabeceras  →  Sin X-Powered-By; Server sin número de versión</t>
+        </is>
+      </c>
+      <c r="I206" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J206" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K206" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L206" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M206" s="7" t="inlineStr">
+        <is>
+          <t>Server: Kestrel, sin X-Powered-By.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
+        <is>
+          <t>TC-206</t>
+        </is>
+      </c>
+      <c r="B207" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C207" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="inlineStr">
+        <is>
+          <t>Payload de 2 MB y JSON malformado</t>
+        </is>
+      </c>
+      <c r="E207" s="7" t="inlineStr">
+        <is>
+          <t>La API rechaza entradas anómalas sin romperse ni filtrar trazas.</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H207" s="7" t="inlineStr">
+        <is>
+          <t>1. POST con un nombre de 2 MB  →  4xx
+2. POST con JSON incompleto  →  400 sin stack trace</t>
+        </is>
+      </c>
+      <c r="I207" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J207" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K207" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L207" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M207" s="7" t="inlineStr">
+        <is>
+          <t>2 MB: 400. JSON malformado: 400 sin trazas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
+        <is>
+          <t>TC-207</t>
+        </is>
+      </c>
+      <c r="B208" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C208" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>Ids inexistentes o mal formados</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
+          <t>Sin errores 500 ni datos de otros registros.</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H208" s="7" t="inlineStr">
+        <is>
+          <t>1. GET de una ficha con un GUID inexistente  →  404
+2. GET con un id mal formado ('1;DROP')  →  4xx</t>
+        </is>
+      </c>
+      <c r="I208" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J208" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K208" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L208" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M208" s="7" t="inlineStr">
+        <is>
+          <t>Inexistente: 404. Mal formado: 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>TC-208</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>Carga: listado de fichas</t>
+        </is>
+      </c>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>50 usuarios concurrentes consultando el listado.</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>1. 500 pedidos GET api/social-records/list con 50 en paralelo  →  Sin errores y p95 &lt; 2000 ms</t>
+        </is>
+      </c>
+      <c r="I209" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K209" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L209" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M209" s="7" t="inlineStr">
+        <is>
+          <t>Listado de fichas: 50 usuarios concurrentes, 500 pedidos, 0 errores, 486.9 pedidos/s, p50 89 ms, p95 195 ms, máximo 318 ms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
+        <is>
+          <t>TC-209</t>
+        </is>
+      </c>
+      <c r="B210" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C210" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>Carga: notificaciones</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
+          <t>50 usuarios concurrentes consultando notificaciones.</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>1. 500 pedidos GET api/notifications con 50 en paralelo  →  Sin errores y p95 &lt; 2000 ms</t>
+        </is>
+      </c>
+      <c r="I210" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J210" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K210" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L210" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M210" s="7" t="inlineStr">
+        <is>
+          <t>Notificaciones: 50 usuarios concurrentes, 500 pedidos, 0 errores, 756.9 pedidos/s, p50 62 ms, p95 101 ms, máximo 161 ms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t>TC-210</t>
+        </is>
+      </c>
+      <c r="B211" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C211" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D211" s="7" t="inlineStr">
+        <is>
+          <t>Carga: calendario general</t>
+        </is>
+      </c>
+      <c r="E211" s="7" t="inlineStr">
+        <is>
+          <t>30 usuarios concurrentes consultando el calendario.</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>1. 300 pedidos GET api/general-calendar-events con 30 en paralelo  →  Sin errores y p95 &lt; 2000 ms</t>
+        </is>
+      </c>
+      <c r="I211" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J211" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K211" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L211" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M211" s="7" t="inlineStr">
+        <is>
+          <t>Calendario general: 30 usuarios concurrentes, 300 pedidos, 0 errores, 545.1 pedidos/s, p50 49 ms, p95 89 ms, máximo 101 ms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
+        <is>
+          <t>TC-211</t>
+        </is>
+      </c>
+      <c r="B212" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="C212" s="7" t="inlineStr">
+        <is>
+          <t>Seguridad y rendimiento</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>Carga: inicio de sesión</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
+          <t>20 usuarios concurrentes iniciando sesión (bcrypt).</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>Stack local levantado (docker compose en backend/); usuarios de prueba *@test.com.</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>RNF seguridad / rendimiento</t>
+        </is>
+      </c>
+      <c r="H212" s="7" t="inlineStr">
+        <is>
+          <t>1. 100 pedidos POST api/auth/login con 20 en paralelo  →  Sin errores y p95 &lt; 3000 ms</t>
+        </is>
+      </c>
+      <c r="I212" s="7" t="inlineStr">
+        <is>
+          <t>docs/qa/security/api-security-and-load.mjs</t>
+        </is>
+      </c>
+      <c r="J212" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="K212" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="L212" s="7" t="inlineStr">
+        <is>
+          <t>Mateo Pavoni</t>
+        </is>
+      </c>
+      <c r="M212" s="7" t="inlineStr">
+        <is>
+          <t>Login: 20 usuarios concurrentes, 100 pedidos, 0 errores, 11.6 pedidos/s, p50 1674 ms, p95 2781 ms, máximo 3110 ms.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M195"/>
+  <autoFilter ref="A1:M212"/>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J195" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J212" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pendiente,OK,Falla,Bloqueado"</formula1>
     </dataValidation>
   </dataValidations>
@@ -42606,7 +43984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -42780,7 +44158,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Los ítems del menú Inicio, Asistencia, Medicación e Informes apuntan a /inicio, una ruta sin pantalla (página vacía). Está en main.</t>
+          <t>Los ítems Inicio, Asistencia y Medicación ya funcionan; solo 'Informes' apunta a /inicio, una ruta sin pantalla (página vacía). Verificado en navegador con los 4 roles el 2026-10-16.</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -43279,8 +44657,248 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Defecto</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Cuenta bloqueada: el login navegaba a /auth/blocked, una ruta que no existe, y dejaba la pantalla en blanco sin ningún mensaje.</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-84 / 94 (frontend)</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Corregido en dev</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>login.component.ts ahora muestra el aviso de bloqueo en el propio formulario. Re-ejecutado OK en navegador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Defecto</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>El quinto intento fallido de login bloqueaba la cuenta pero respondía 401 'Credenciales inválidas': no informaba el bloqueo hasta el sexto intento.</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-84 (AuthService)</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Corregido en dev</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>AuthService.LoginAsync devuelve AccountLocked en el intento que dispara el bloqueo; test unitario nuevo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Defecto</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Una cuenta desactivada que intentaba ingresar veía 'No pudimos iniciar sesión. Probá de nuevo en unos minutos.' (el frontend no mapeaba el estado Inactive de la API).</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-20 (frontend)</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Corregido en dev</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>AuthService.mapError distingue Inactive y Rejected; mensajes específicos y tests nuevos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Defecto</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Al guardar una ficha con fecha futura la UI mostraba el mensaje genérico 'Ocurrió un error al guardar la ficha.' aunque la API devolvía 'La fecha de ingreso no puede ser futura.'.</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-5 (frontend)</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Corregido en dev</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Las pantallas de alta y edición usan extractApiError y muestran el motivo de validación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Defecto</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>El rol Escucha veía el botón 'Editar ficha' en el detalle y el ícono de editar en el listado (la ruta /edit sí lo rechazaba con acceso denegado).</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-13 / 64 (frontend)</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Corregido en dev</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>Ambos controles se muestran solo con el permiso fichas.edit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Defecto</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Una observación con solo espacios habilitaba el botón Guardar; el backend la rechazaba con 400.</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-9 (frontend)</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Corregido en dev</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>El formulario valida el largo mínimo sobre el texto recortado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>La API acepta crear dos fichas con el mismo DNI (201 y 201). Los colaboradores sí rechazan DNI duplicado (409).</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-5 / EP-01</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>Confirmar si el DNI debe ser único en fichas antes de agregar la regla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Pregunta abierta</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>La API permite crear fichas al Coordinador de Casa de Convivencia (POST api/social-records), pero la UI le deniega /fichas/crear.</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>SCRUM-13 / 64</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Se suma a la pregunta #20 sobre los permisos del Coordinador.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A1:F30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>